--- a/reasignacion_st_detallada.xlsx
+++ b/reasignacion_st_detallada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B386B710-AE22-B241-A486-4EFBC3CF3F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3D8183-6C8C-9D4D-AB41-DB3762BAD205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reclasifiación ST" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="256" r:id="rId3"/>
+    <pivotCache cacheId="270" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2025" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="506">
   <si>
     <t>OT</t>
   </si>
@@ -1843,6 +1843,36 @@
   </si>
   <si>
     <t>Adi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galileo estación reelevadora </t>
+  </si>
+  <si>
+    <t>Gestiones</t>
+  </si>
+  <si>
+    <t>Visita terreno</t>
+  </si>
+  <si>
+    <t>Configuración telemetria pozo BN12</t>
+  </si>
+  <si>
+    <t>Se acude al punto a verificar la condición y se anota lo que falta para la habilitación de éste.
+Batería acorde y peinado de cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Se coordina con Joanil Contreras para la entrega de perfil metálico para instalación de lector de velocidad RQ30.
+- Se hace entrega de documentación a Sr. Nicolas solicitado por Rodrigo López.
+- Se espero a don Diego Ramos para la verificación de instalación de los postes en los puntos PEM, pero no fue posible reunirnos, esta coordinado para hoy a las 10:00hrs apox.
+- Se rotula las herramientas acorde al color reactivo de este mes. </t>
+  </si>
+  <si>
+    <t>Se intstala sensor de nivel en pozo y se configura el equipo junto con el flujometro a traves de lecturas modbus, se comprueban valores en PLC.
+Por otro lado se configura la comunicación del punto a la telemetria WeTechs para la visualizacion de datos.
+Adicionalmente se instalan equipos de comunicación para la lectura de datos a través de red LORA.</t>
   </si>
 </sst>
 </file>
@@ -2023,7 +2053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2051,6 +2081,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2073,6 +2105,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2082,166 +2123,48 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="340">
+  <dxfs count="104">
     <dxf>
-      <border>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
       <border>
@@ -2820,29 +2743,46 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2855,9 +2795,17 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -2892,17 +2840,9 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2915,60 +2855,7 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <border>
@@ -2993,7 +2880,60 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3006,9 +2946,17 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -3043,17 +2991,9 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
+      <font>
+        <b/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3066,46 +3006,7 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <border>
@@ -3128,1863 +3029,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5134,9 +3178,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2">
-              <a:lumMod val="60000"/>
-            </a:schemeClr>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5195,9 +3237,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:lumMod val="60000"/>
-            </a:schemeClr>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5256,7 +3296,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent5"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5374,7 +3414,7 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5433,7 +3473,7 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5492,7 +3532,7 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent4"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -5546,6 +3586,20 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -5724,6 +3778,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5BC5-BF4C-9D30-781F705AEBD1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
@@ -5868,6 +3927,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-5BC5-BF4C-9D30-781F705AEBD1}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -6672,7 +4734,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daniel Cuero" refreshedDate="46028.684331712961" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="247" xr:uid="{0361626B-1122-CE47-8D2B-862A439D0806}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daniel Cuero" refreshedDate="46029.494483796298" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="247" xr:uid="{0361626B-1122-CE47-8D2B-862A439D0806}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J248" sheet="reclasifiación ST"/>
   </cacheSource>
@@ -9722,251 +7784,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="256" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item m="1" x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item m="1" x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="7"/>
-  </colFields>
-  <colItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="18">
-    <format dxfId="186">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="187">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="188">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="189">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="190">
-      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="191">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="192">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="193">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="194">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="195">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="196">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="197">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="198">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="199">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="200">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="201">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="202">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="203">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="256" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -10031,7 +7849,7 @@
   <dataFields count="1">
     <dataField name="Cuenta de Fecha" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="8">
+  <chartFormats count="9">
     <chartFormat chart="4" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10125,6 +7943,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="4" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -10138,8 +7968,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="256" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="F22:O34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -10272,41 +8102,41 @@
     <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="170">
+    <format dxfId="85">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="171">
+    <format dxfId="84">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="172">
+    <format dxfId="83">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="173">
+    <format dxfId="82">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="174">
+    <format dxfId="81">
       <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="175">
+    <format dxfId="80">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="176">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="177">
+    <format dxfId="78">
       <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="178">
+    <format dxfId="77">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="179">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="180">
+    <format dxfId="75">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -10315,7 +8145,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="181">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -10324,7 +8154,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="182">
+    <format dxfId="73">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -10333,7 +8163,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="183">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -10342,7 +8172,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="184">
+    <format dxfId="71">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -10351,7 +8181,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="185">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -10371,6 +8201,272 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item m="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item m="1" x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="18">
+    <format dxfId="103">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="102">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="101">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="100">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="99">
+      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="98">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="97">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="96">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="95">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="94">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="93">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="92">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="91">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="90">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="89">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="88">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="87">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="86">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD993EFB-D955-5C4E-A71F-DA84C3008DB7}" name="Tabla1" displayName="Tabla1" ref="A1:J251" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:J251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J251">
+    <sortCondition ref="A1:A251"/>
+  </sortState>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{6DD74F18-117A-EE4B-8437-4D852508B413}" name="OT"/>
+    <tableColumn id="2" xr3:uid="{AC558773-13A8-3048-A577-0E4AC7D5F8AC}" name="Fecha" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{79DD1F73-91E5-234C-B201-3293AC0C4C8A}" name="Técnico"/>
+    <tableColumn id="4" xr3:uid="{FC81FE9D-F306-0D4A-BF0C-AA6091B1C2E3}" name="Cliente"/>
+    <tableColumn id="5" xr3:uid="{951FF7CA-73A7-C14A-93D5-BEF519DFDEAA}" name="Proyecto"/>
+    <tableColumn id="6" xr3:uid="{AD47ADDB-80FD-214F-AE19-C26DDD7B232D}" name="Asset"/>
+    <tableColumn id="7" xr3:uid="{2818D171-75A5-3343-BE8F-8BE52C8AFFAB}" name="Tipo de trabajo anterior"/>
+    <tableColumn id="8" xr3:uid="{BA12CF4D-FDDA-684B-99BF-F9181DC3E80E}" name="Tipo de trabajo nuevo"/>
+    <tableColumn id="9" xr3:uid="{C90768FC-7C74-1644-9002-F34519EF6B25}" name="Causa visita"/>
+    <tableColumn id="10" xr3:uid="{3BCE3010-FC70-2547-95FC-57FAD7174575}" name="Resolución"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10658,7 +8754,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10667,9 +8762,10 @@
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="34.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="58.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" customWidth="1"/>
     <col min="9" max="9" width="71.5" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -10704,7 +8800,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>78</v>
       </c>
@@ -10736,7 +8832,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>81</v>
       </c>
@@ -10768,7 +8864,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>81</v>
       </c>
@@ -10800,7 +8896,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>83</v>
       </c>
@@ -10829,7 +8925,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>93</v>
       </c>
@@ -10861,7 +8957,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>93</v>
       </c>
@@ -10893,7 +8989,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>94</v>
       </c>
@@ -10925,7 +9021,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>94</v>
       </c>
@@ -10957,7 +9053,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>94</v>
       </c>
@@ -10989,7 +9085,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>94</v>
       </c>
@@ -11021,7 +9117,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>95</v>
       </c>
@@ -11053,7 +9149,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>96</v>
       </c>
@@ -11085,7 +9181,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>97</v>
       </c>
@@ -11117,7 +9213,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>101</v>
       </c>
@@ -11149,7 +9245,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>101</v>
       </c>
@@ -11181,7 +9277,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>101</v>
       </c>
@@ -11213,7 +9309,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>101</v>
       </c>
@@ -11245,7 +9341,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>101</v>
       </c>
@@ -11277,7 +9373,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>105</v>
       </c>
@@ -11309,7 +9405,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>105</v>
       </c>
@@ -11341,7 +9437,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>110</v>
       </c>
@@ -11373,7 +9469,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>110</v>
       </c>
@@ -11405,7 +9501,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>110</v>
       </c>
@@ -11437,7 +9533,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>111</v>
       </c>
@@ -11469,7 +9565,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>111</v>
       </c>
@@ -11501,7 +9597,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>111</v>
       </c>
@@ -11533,7 +9629,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>114</v>
       </c>
@@ -11565,7 +9661,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>114</v>
       </c>
@@ -11597,7 +9693,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>115</v>
       </c>
@@ -11629,7 +9725,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>115</v>
       </c>
@@ -11661,7 +9757,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>115</v>
       </c>
@@ -11693,7 +9789,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>117</v>
       </c>
@@ -11725,7 +9821,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>118</v>
       </c>
@@ -11757,7 +9853,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>118</v>
       </c>
@@ -11789,7 +9885,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>119</v>
       </c>
@@ -11821,7 +9917,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>123</v>
       </c>
@@ -11853,7 +9949,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>123</v>
       </c>
@@ -11885,7 +9981,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>126</v>
       </c>
@@ -11914,7 +10010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>126</v>
       </c>
@@ -11943,7 +10039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>130</v>
       </c>
@@ -11975,7 +10071,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>130</v>
       </c>
@@ -12007,7 +10103,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>132</v>
       </c>
@@ -12039,7 +10135,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>143</v>
       </c>
@@ -12071,7 +10167,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>148</v>
       </c>
@@ -12100,7 +10196,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>148</v>
       </c>
@@ -12129,7 +10225,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>148</v>
       </c>
@@ -12158,7 +10254,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>148</v>
       </c>
@@ -12187,7 +10283,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>148</v>
       </c>
@@ -12216,7 +10312,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>148</v>
       </c>
@@ -12245,7 +10341,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>153</v>
       </c>
@@ -12277,7 +10373,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>153</v>
       </c>
@@ -12309,7 +10405,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>153</v>
       </c>
@@ -12341,7 +10437,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>155</v>
       </c>
@@ -12373,7 +10469,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>163</v>
       </c>
@@ -12405,7 +10501,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>163</v>
       </c>
@@ -12437,7 +10533,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>163</v>
       </c>
@@ -12469,7 +10565,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>164</v>
       </c>
@@ -12501,7 +10597,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>166</v>
       </c>
@@ -12533,7 +10629,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>168</v>
       </c>
@@ -12562,7 +10658,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>172</v>
       </c>
@@ -12591,7 +10687,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>172</v>
       </c>
@@ -12620,7 +10716,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>172</v>
       </c>
@@ -12649,7 +10745,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>175</v>
       </c>
@@ -12681,7 +10777,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>175</v>
       </c>
@@ -12713,7 +10809,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>175</v>
       </c>
@@ -12745,7 +10841,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>175</v>
       </c>
@@ -12777,7 +10873,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>176</v>
       </c>
@@ -12809,7 +10905,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>176</v>
       </c>
@@ -12841,7 +10937,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>176</v>
       </c>
@@ -12873,7 +10969,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>179</v>
       </c>
@@ -12905,7 +11001,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>180</v>
       </c>
@@ -12937,7 +11033,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>182</v>
       </c>
@@ -12969,7 +11065,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>183</v>
       </c>
@@ -13001,7 +11097,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>187</v>
       </c>
@@ -13033,7 +11129,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>187</v>
       </c>
@@ -13065,7 +11161,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>187</v>
       </c>
@@ -13097,7 +11193,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>187</v>
       </c>
@@ -13129,7 +11225,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>190</v>
       </c>
@@ -13161,7 +11257,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>191</v>
       </c>
@@ -13193,7 +11289,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>191</v>
       </c>
@@ -13225,7 +11321,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>191</v>
       </c>
@@ -13257,7 +11353,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>191</v>
       </c>
@@ -13289,7 +11385,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>192</v>
       </c>
@@ -13321,7 +11417,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>194</v>
       </c>
@@ -13353,7 +11449,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>196</v>
       </c>
@@ -13385,7 +11481,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>196</v>
       </c>
@@ -13417,7 +11513,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>196</v>
       </c>
@@ -13449,7 +11545,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>196</v>
       </c>
@@ -13481,7 +11577,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>199</v>
       </c>
@@ -13513,7 +11609,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>202</v>
       </c>
@@ -13545,7 +11641,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>205</v>
       </c>
@@ -13577,7 +11673,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>206</v>
       </c>
@@ -13609,7 +11705,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>213</v>
       </c>
@@ -13641,7 +11737,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>214</v>
       </c>
@@ -13673,7 +11769,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>217</v>
       </c>
@@ -13705,7 +11801,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>217</v>
       </c>
@@ -13737,7 +11833,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>217</v>
       </c>
@@ -13769,7 +11865,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>217</v>
       </c>
@@ -13801,7 +11897,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>217</v>
       </c>
@@ -13833,7 +11929,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>217</v>
       </c>
@@ -13865,7 +11961,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>219</v>
       </c>
@@ -13897,7 +11993,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>219</v>
       </c>
@@ -13929,7 +12025,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>219</v>
       </c>
@@ -13961,7 +12057,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>219</v>
       </c>
@@ -13993,7 +12089,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>223</v>
       </c>
@@ -14025,7 +12121,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>223</v>
       </c>
@@ -14057,7 +12153,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>223</v>
       </c>
@@ -14089,7 +12185,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>223</v>
       </c>
@@ -14121,7 +12217,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>231</v>
       </c>
@@ -14153,7 +12249,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>233</v>
       </c>
@@ -14185,7 +12281,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>233</v>
       </c>
@@ -14217,7 +12313,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>233</v>
       </c>
@@ -14249,7 +12345,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>233</v>
       </c>
@@ -14281,7 +12377,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>234</v>
       </c>
@@ -14313,7 +12409,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>236</v>
       </c>
@@ -14345,7 +12441,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>236</v>
       </c>
@@ -14377,7 +12473,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>240</v>
       </c>
@@ -14409,7 +12505,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>240</v>
       </c>
@@ -14441,7 +12537,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>242</v>
       </c>
@@ -14473,7 +12569,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>242</v>
       </c>
@@ -14505,7 +12601,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>242</v>
       </c>
@@ -14537,7 +12633,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>242</v>
       </c>
@@ -14569,7 +12665,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>242</v>
       </c>
@@ -14601,7 +12697,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>244</v>
       </c>
@@ -14633,7 +12729,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>244</v>
       </c>
@@ -14665,7 +12761,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>246</v>
       </c>
@@ -14697,7 +12793,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>246</v>
       </c>
@@ -14729,7 +12825,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>249</v>
       </c>
@@ -14761,7 +12857,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>253</v>
       </c>
@@ -14793,7 +12889,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>253</v>
       </c>
@@ -14825,7 +12921,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>254</v>
       </c>
@@ -14857,7 +12953,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>255</v>
       </c>
@@ -14889,7 +12985,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>255</v>
       </c>
@@ -14921,7 +13017,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>258</v>
       </c>
@@ -14953,7 +13049,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>258</v>
       </c>
@@ -15017,7 +13113,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>262</v>
       </c>
@@ -15049,7 +13145,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>262</v>
       </c>
@@ -15081,7 +13177,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>266</v>
       </c>
@@ -15113,7 +13209,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>266</v>
       </c>
@@ -15145,7 +13241,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>266</v>
       </c>
@@ -15177,7 +13273,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>266</v>
       </c>
@@ -15209,7 +13305,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>267</v>
       </c>
@@ -15241,7 +13337,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>267</v>
       </c>
@@ -15273,7 +13369,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>268</v>
       </c>
@@ -15305,7 +13401,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>272</v>
       </c>
@@ -15337,7 +13433,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>272</v>
       </c>
@@ -15369,7 +13465,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>272</v>
       </c>
@@ -15401,7 +13497,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>272</v>
       </c>
@@ -15433,7 +13529,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>272</v>
       </c>
@@ -15465,7 +13561,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>276</v>
       </c>
@@ -15494,7 +13590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>276</v>
       </c>
@@ -15523,7 +13619,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>276</v>
       </c>
@@ -15555,7 +13651,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>278</v>
       </c>
@@ -15587,7 +13683,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>278</v>
       </c>
@@ -15619,7 +13715,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>278</v>
       </c>
@@ -15651,7 +13747,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>283</v>
       </c>
@@ -15683,7 +13779,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>283</v>
       </c>
@@ -15715,7 +13811,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>283</v>
       </c>
@@ -15747,7 +13843,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>287</v>
       </c>
@@ -15779,7 +13875,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>288</v>
       </c>
@@ -15811,7 +13907,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>288</v>
       </c>
@@ -15843,7 +13939,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>288</v>
       </c>
@@ -15875,7 +13971,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>288</v>
       </c>
@@ -15907,7 +14003,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>288</v>
       </c>
@@ -15939,7 +14035,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>288</v>
       </c>
@@ -15971,7 +14067,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>289</v>
       </c>
@@ -16003,7 +14099,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>290</v>
       </c>
@@ -16035,7 +14131,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>290</v>
       </c>
@@ -16067,7 +14163,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>292</v>
       </c>
@@ -16099,7 +14195,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>292</v>
       </c>
@@ -16131,7 +14227,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>292</v>
       </c>
@@ -16163,7 +14259,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>292</v>
       </c>
@@ -16195,7 +14291,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>295</v>
       </c>
@@ -16227,7 +14323,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>296</v>
       </c>
@@ -16259,7 +14355,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>296</v>
       </c>
@@ -16291,7 +14387,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>296</v>
       </c>
@@ -16323,7 +14419,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>296</v>
       </c>
@@ -16355,7 +14451,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>296</v>
       </c>
@@ -16387,7 +14483,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>299</v>
       </c>
@@ -16419,7 +14515,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>299</v>
       </c>
@@ -16451,7 +14547,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>299</v>
       </c>
@@ -16483,7 +14579,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>300</v>
       </c>
@@ -16515,7 +14611,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>300</v>
       </c>
@@ -16547,7 +14643,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>302</v>
       </c>
@@ -16579,7 +14675,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>302</v>
       </c>
@@ -16611,7 +14707,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>302</v>
       </c>
@@ -16643,7 +14739,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>302</v>
       </c>
@@ -16675,7 +14771,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>302</v>
       </c>
@@ -16707,7 +14803,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>305</v>
       </c>
@@ -16739,7 +14835,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>306</v>
       </c>
@@ -16771,7 +14867,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>306</v>
       </c>
@@ -16803,7 +14899,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>308</v>
       </c>
@@ -16835,7 +14931,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>309</v>
       </c>
@@ -16867,7 +14963,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>310</v>
       </c>
@@ -16899,7 +14995,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>310</v>
       </c>
@@ -16931,7 +15027,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>311</v>
       </c>
@@ -16963,7 +15059,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>312</v>
       </c>
@@ -16995,7 +15091,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>312</v>
       </c>
@@ -17027,7 +15123,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>312</v>
       </c>
@@ -17059,7 +15155,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>312</v>
       </c>
@@ -17091,7 +15187,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>313</v>
       </c>
@@ -17123,7 +15219,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>313</v>
       </c>
@@ -17155,7 +15251,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>313</v>
       </c>
@@ -17187,7 +15283,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>313</v>
       </c>
@@ -17219,7 +15315,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>314</v>
       </c>
@@ -17251,7 +15347,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>315</v>
       </c>
@@ -17283,7 +15379,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>315</v>
       </c>
@@ -17315,7 +15411,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>318</v>
       </c>
@@ -17347,7 +15443,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>318</v>
       </c>
@@ -17379,7 +15475,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>320</v>
       </c>
@@ -17411,7 +15507,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>321</v>
       </c>
@@ -17443,7 +15539,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>321</v>
       </c>
@@ -17475,7 +15571,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>325</v>
       </c>
@@ -17507,7 +15603,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>326</v>
       </c>
@@ -17539,7 +15635,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>327</v>
       </c>
@@ -17571,7 +15667,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>327</v>
       </c>
@@ -17603,7 +15699,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>330</v>
       </c>
@@ -17635,7 +15731,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>334</v>
       </c>
@@ -17667,7 +15763,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>336</v>
       </c>
@@ -17699,7 +15795,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>338</v>
       </c>
@@ -17728,7 +15824,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>338</v>
       </c>
@@ -17757,7 +15853,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>339</v>
       </c>
@@ -17786,7 +15882,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>339</v>
       </c>
@@ -17815,7 +15911,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>339</v>
       </c>
@@ -17844,7 +15940,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>339</v>
       </c>
@@ -17873,7 +15969,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>340</v>
       </c>
@@ -17905,39 +16001,39 @@
         <v>462</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="33">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A229" s="17">
         <v>341</v>
       </c>
-      <c r="B229" s="34">
+      <c r="B229" s="18">
         <v>46009</v>
       </c>
-      <c r="C229" s="33" t="s">
+      <c r="C229" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D229" s="33" t="s">
+      <c r="D229" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="E229" s="33" t="s">
+      <c r="E229" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F229" s="33" t="s">
+      <c r="F229" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G229" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H229" s="33" t="s">
+      <c r="G229" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H229" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I229" s="33" t="s">
+      <c r="I229" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="J229" s="33" t="s">
+      <c r="J229" s="17" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>342</v>
       </c>
@@ -17969,7 +16065,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>342</v>
       </c>
@@ -18001,575 +16097,651 @@
         <v>465</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="33" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="35">
+    <row r="232" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A232">
         <v>345</v>
       </c>
-      <c r="B232" s="36">
+      <c r="B232" s="4">
         <v>46014</v>
       </c>
-      <c r="C232" s="35" t="s">
+      <c r="C232" t="s">
         <v>20</v>
       </c>
-      <c r="D232" s="35" t="s">
+      <c r="D232" t="s">
         <v>254</v>
       </c>
-      <c r="E232" s="35" t="s">
+      <c r="E232" t="s">
         <v>466</v>
       </c>
-      <c r="F232" s="35" t="s">
+      <c r="F232" t="s">
         <v>467</v>
       </c>
-      <c r="G232" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H232" s="35" t="s">
+      <c r="G232" t="s">
+        <v>10</v>
+      </c>
+      <c r="H232" t="s">
         <v>203</v>
       </c>
-      <c r="I232" s="35" t="s">
+      <c r="I232" t="s">
         <v>475</v>
       </c>
-      <c r="J232" s="35" t="s">
+      <c r="J232" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A233">
         <v>347</v>
       </c>
-      <c r="B233" s="36">
+      <c r="B233" s="4">
         <v>46013</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="C233" t="s">
         <v>7</v>
       </c>
-      <c r="D233" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E233" s="35" t="s">
+      <c r="D233" t="s">
+        <v>209</v>
+      </c>
+      <c r="E233" t="s">
         <v>13</v>
       </c>
-      <c r="F233" s="35" t="s">
+      <c r="F233" t="s">
         <v>54</v>
       </c>
-      <c r="G233" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H233" s="35" t="s">
+      <c r="G233" t="s">
+        <v>10</v>
+      </c>
+      <c r="H233" t="s">
         <v>11</v>
       </c>
-      <c r="I233" s="35" t="s">
+      <c r="I233" t="s">
         <v>12</v>
       </c>
-      <c r="J233" s="35" t="s">
+      <c r="J233" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="35">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A234">
         <v>348</v>
       </c>
-      <c r="B234" s="36">
+      <c r="B234" s="4">
         <v>46014</v>
       </c>
-      <c r="C234" s="35" t="s">
+      <c r="C234" t="s">
         <v>107</v>
       </c>
-      <c r="D234" s="35" t="s">
+      <c r="D234" t="s">
         <v>257</v>
       </c>
-      <c r="E234" s="35" t="s">
+      <c r="E234" t="s">
         <v>122</v>
       </c>
-      <c r="F234" s="35" t="s">
+      <c r="F234" t="s">
         <v>201</v>
       </c>
-      <c r="G234" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H234" s="35" t="s">
+      <c r="G234" t="s">
+        <v>10</v>
+      </c>
+      <c r="H234" t="s">
         <v>28</v>
       </c>
-      <c r="I234" s="35" t="s">
+      <c r="I234" t="s">
         <v>476</v>
       </c>
-      <c r="J234" s="35" t="s">
+      <c r="J234" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="235" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="35">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A235">
         <v>349</v>
       </c>
-      <c r="B235" s="36">
+      <c r="B235" s="4">
         <v>46014</v>
       </c>
-      <c r="C235" s="35" t="s">
+      <c r="C235" t="s">
         <v>43</v>
       </c>
-      <c r="D235" s="35" t="s">
+      <c r="D235" t="s">
         <v>254</v>
       </c>
-      <c r="E235" s="35" t="s">
+      <c r="E235" t="s">
         <v>467</v>
       </c>
-      <c r="F235" s="35" t="s">
+      <c r="F235" t="s">
         <v>469</v>
       </c>
-      <c r="G235" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H235" s="35" t="s">
+      <c r="G235" t="s">
+        <v>10</v>
+      </c>
+      <c r="H235" t="s">
         <v>45</v>
       </c>
-      <c r="I235" s="35" t="s">
+      <c r="I235" t="s">
         <v>477</v>
       </c>
-      <c r="J235" s="35" t="s">
+      <c r="J235" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="236" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="35">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A236">
         <v>351</v>
       </c>
-      <c r="B236" s="36">
+      <c r="B236" s="4">
         <v>46014</v>
       </c>
-      <c r="C236" s="35" t="s">
+      <c r="C236" t="s">
         <v>7</v>
       </c>
-      <c r="D236" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E236" s="35" t="s">
+      <c r="D236" t="s">
+        <v>209</v>
+      </c>
+      <c r="E236" t="s">
         <v>8</v>
       </c>
-      <c r="F236" s="35" t="s">
+      <c r="F236" t="s">
         <v>470</v>
       </c>
-      <c r="G236" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H236" s="35" t="s">
+      <c r="G236" t="s">
+        <v>10</v>
+      </c>
+      <c r="H236" t="s">
         <v>203</v>
       </c>
-      <c r="I236" s="35" t="s">
+      <c r="I236" t="s">
         <v>12</v>
       </c>
-      <c r="J236" s="35" t="s">
+      <c r="J236" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="237" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A237">
         <v>351</v>
       </c>
-      <c r="B237" s="36">
+      <c r="B237" s="4">
         <v>46014</v>
       </c>
-      <c r="C237" s="35" t="s">
+      <c r="C237" t="s">
         <v>7</v>
       </c>
-      <c r="D237" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E237" s="35" t="s">
+      <c r="D237" t="s">
+        <v>209</v>
+      </c>
+      <c r="E237" t="s">
         <v>13</v>
       </c>
-      <c r="F237" s="35" t="s">
+      <c r="F237" t="s">
         <v>53</v>
       </c>
-      <c r="G237" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H237" s="35" t="s">
+      <c r="G237" t="s">
+        <v>10</v>
+      </c>
+      <c r="H237" t="s">
         <v>11</v>
       </c>
-      <c r="I237" s="35" t="s">
+      <c r="I237" t="s">
         <v>12</v>
       </c>
-      <c r="J237" s="35" t="s">
+      <c r="J237" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="238" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A238">
         <v>353</v>
       </c>
-      <c r="B238" s="36">
+      <c r="B238" s="4">
         <v>46016</v>
       </c>
-      <c r="C238" s="35" t="s">
+      <c r="C238" t="s">
         <v>7</v>
       </c>
-      <c r="D238" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E238" s="35" t="s">
+      <c r="D238" t="s">
+        <v>209</v>
+      </c>
+      <c r="E238" t="s">
         <v>13</v>
       </c>
-      <c r="F238" s="35" t="s">
+      <c r="F238" t="s">
         <v>51</v>
       </c>
-      <c r="G238" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H238" s="35" t="s">
+      <c r="G238" t="s">
+        <v>10</v>
+      </c>
+      <c r="H238" t="s">
         <v>11</v>
       </c>
-      <c r="I238" s="35" t="s">
+      <c r="I238" t="s">
         <v>12</v>
       </c>
-      <c r="J238" s="35" t="s">
+      <c r="J238" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="239" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="35">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A239">
         <v>355</v>
       </c>
-      <c r="B239" s="36">
+      <c r="B239" s="4">
         <v>46017</v>
       </c>
-      <c r="C239" s="35" t="s">
+      <c r="C239" t="s">
         <v>7</v>
       </c>
-      <c r="D239" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E239" s="35" t="s">
+      <c r="D239" t="s">
+        <v>209</v>
+      </c>
+      <c r="E239" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="35" t="s">
+      <c r="F239" t="s">
         <v>89</v>
       </c>
-      <c r="G239" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H239" s="35" t="s">
+      <c r="G239" t="s">
+        <v>10</v>
+      </c>
+      <c r="H239" t="s">
         <v>203</v>
       </c>
-      <c r="I239" s="35" t="s">
+      <c r="I239" t="s">
         <v>12</v>
       </c>
-      <c r="J239" s="35" t="s">
+      <c r="J239" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="240" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="35">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A240">
         <v>356</v>
       </c>
-      <c r="B240" s="36">
+      <c r="B240" s="4">
         <v>46015</v>
       </c>
-      <c r="C240" s="35" t="s">
+      <c r="C240" t="s">
         <v>43</v>
       </c>
-      <c r="D240" s="35" t="s">
+      <c r="D240" t="s">
         <v>254</v>
       </c>
-      <c r="E240" s="35" t="s">
+      <c r="E240" t="s">
         <v>48</v>
       </c>
-      <c r="F240" s="35" t="s">
+      <c r="F240" t="s">
         <v>471</v>
       </c>
-      <c r="G240" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H240" s="35" t="s">
+      <c r="G240" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" t="s">
         <v>45</v>
       </c>
-      <c r="I240" s="35" t="s">
+      <c r="I240" t="s">
         <v>478</v>
       </c>
-      <c r="J240" s="35" t="s">
+      <c r="J240" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="241" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="35">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A241">
         <v>357</v>
       </c>
-      <c r="B241" s="36">
+      <c r="B241" s="4">
         <v>46020</v>
       </c>
-      <c r="C241" s="35" t="s">
+      <c r="C241" t="s">
         <v>7</v>
       </c>
-      <c r="D241" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E241" s="35" t="s">
+      <c r="D241" t="s">
+        <v>209</v>
+      </c>
+      <c r="E241" t="s">
         <v>8</v>
       </c>
-      <c r="F241" s="35" t="s">
+      <c r="F241" t="s">
         <v>472</v>
       </c>
-      <c r="G241" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H241" s="35" t="s">
+      <c r="G241" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" t="s">
         <v>45</v>
       </c>
-      <c r="I241" s="35" t="s">
+      <c r="I241" t="s">
         <v>12</v>
       </c>
-      <c r="J241" s="35" t="s">
+      <c r="J241" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="242" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="35">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A242">
         <v>357</v>
       </c>
-      <c r="B242" s="36">
+      <c r="B242" s="4">
         <v>46020</v>
       </c>
-      <c r="C242" s="35" t="s">
+      <c r="C242" t="s">
         <v>7</v>
       </c>
-      <c r="D242" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E242" s="35" t="s">
+      <c r="D242" t="s">
+        <v>209</v>
+      </c>
+      <c r="E242" t="s">
         <v>13</v>
       </c>
-      <c r="F242" s="35" t="s">
+      <c r="F242" t="s">
         <v>51</v>
       </c>
-      <c r="G242" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H242" s="35" t="s">
+      <c r="G242" t="s">
+        <v>10</v>
+      </c>
+      <c r="H242" t="s">
         <v>25</v>
       </c>
-      <c r="I242" s="35" t="s">
+      <c r="I242" t="s">
         <v>12</v>
       </c>
-      <c r="J242" s="35" t="s">
+      <c r="J242" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="243" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="35">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A243">
         <v>357</v>
       </c>
-      <c r="B243" s="36">
+      <c r="B243" s="4">
         <v>46020</v>
       </c>
-      <c r="C243" s="35" t="s">
+      <c r="C243" t="s">
         <v>7</v>
       </c>
-      <c r="D243" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E243" s="35" t="s">
+      <c r="D243" t="s">
+        <v>209</v>
+      </c>
+      <c r="E243" t="s">
         <v>8</v>
       </c>
-      <c r="F243" s="35" t="s">
+      <c r="F243" t="s">
         <v>472</v>
       </c>
-      <c r="G243" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H243" s="35" t="s">
+      <c r="G243" t="s">
+        <v>10</v>
+      </c>
+      <c r="H243" t="s">
         <v>45</v>
       </c>
-      <c r="I243" s="35" t="s">
+      <c r="I243" t="s">
         <v>12</v>
       </c>
-      <c r="J243" s="35" t="s">
+      <c r="J243" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="35">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A244">
         <v>361</v>
       </c>
-      <c r="B244" s="36">
+      <c r="B244" s="4">
         <v>46021</v>
       </c>
-      <c r="C244" s="35" t="s">
+      <c r="C244" t="s">
         <v>7</v>
       </c>
-      <c r="D244" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E244" s="35" t="s">
+      <c r="D244" t="s">
+        <v>209</v>
+      </c>
+      <c r="E244" t="s">
         <v>8</v>
       </c>
-      <c r="F244" s="35" t="s">
+      <c r="F244" t="s">
         <v>472</v>
       </c>
-      <c r="G244" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H244" s="35" t="s">
+      <c r="G244" t="s">
+        <v>10</v>
+      </c>
+      <c r="H244" t="s">
         <v>496</v>
       </c>
-      <c r="I244" s="35" t="s">
+      <c r="I244" t="s">
         <v>12</v>
       </c>
-      <c r="J244" s="35" t="s">
+      <c r="J244" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="245" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="35">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A245">
         <v>361</v>
       </c>
-      <c r="B245" s="36">
+      <c r="B245" s="4">
         <v>46021</v>
       </c>
-      <c r="C245" s="35" t="s">
+      <c r="C245" t="s">
         <v>7</v>
       </c>
-      <c r="D245" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E245" s="35" t="s">
+      <c r="D245" t="s">
+        <v>209</v>
+      </c>
+      <c r="E245" t="s">
         <v>468</v>
       </c>
-      <c r="F245" s="35" t="s">
+      <c r="F245" t="s">
         <v>473</v>
       </c>
-      <c r="G245" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H245" s="35" t="s">
+      <c r="G245" t="s">
+        <v>10</v>
+      </c>
+      <c r="H245" t="s">
         <v>28</v>
       </c>
-      <c r="I245" s="35" t="s">
+      <c r="I245" t="s">
         <v>12</v>
       </c>
-      <c r="J245" s="35" t="s">
+      <c r="J245" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="246" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="35">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A246">
         <v>365</v>
       </c>
-      <c r="B246" s="36">
+      <c r="B246" s="4">
         <v>46022</v>
       </c>
-      <c r="C246" s="35" t="s">
+      <c r="C246" t="s">
         <v>7</v>
       </c>
-      <c r="D246" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E246" s="35" t="s">
+      <c r="D246" t="s">
+        <v>209</v>
+      </c>
+      <c r="E246" t="s">
         <v>13</v>
       </c>
-      <c r="F246" s="35" t="s">
+      <c r="F246" t="s">
         <v>62</v>
       </c>
-      <c r="G246" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H246" s="35" t="s">
+      <c r="G246" t="s">
+        <v>10</v>
+      </c>
+      <c r="H246" t="s">
         <v>25</v>
       </c>
-      <c r="I246" s="35" t="s">
+      <c r="I246" t="s">
         <v>12</v>
       </c>
-      <c r="J246" s="35" t="s">
+      <c r="J246" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="247" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="35">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A247">
         <v>365</v>
       </c>
-      <c r="B247" s="36">
+      <c r="B247" s="4">
         <v>46022</v>
       </c>
-      <c r="C247" s="35" t="s">
+      <c r="C247" t="s">
         <v>7</v>
       </c>
-      <c r="D247" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E247" s="35" t="s">
+      <c r="D247" t="s">
+        <v>209</v>
+      </c>
+      <c r="E247" t="s">
         <v>8</v>
       </c>
-      <c r="F247" s="35" t="s">
+      <c r="F247" t="s">
         <v>474</v>
       </c>
-      <c r="G247" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H247" s="35" t="s">
+      <c r="G247" t="s">
+        <v>10</v>
+      </c>
+      <c r="H247" t="s">
         <v>60</v>
       </c>
-      <c r="I247" s="35" t="s">
+      <c r="I247" t="s">
         <v>12</v>
       </c>
-      <c r="J247" s="35" t="s">
+      <c r="J247" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="35">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A248">
         <v>365</v>
       </c>
-      <c r="B248" s="36">
+      <c r="B248" s="4">
         <v>46022</v>
       </c>
-      <c r="C248" s="35" t="s">
+      <c r="C248" t="s">
         <v>7</v>
       </c>
-      <c r="D248" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E248" s="35" t="s">
+      <c r="D248" t="s">
+        <v>209</v>
+      </c>
+      <c r="E248" t="s">
         <v>13</v>
       </c>
-      <c r="F248" s="35" t="s">
+      <c r="F248" t="s">
         <v>70</v>
       </c>
-      <c r="G248" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="H248" s="35" t="s">
+      <c r="G248" t="s">
+        <v>10</v>
+      </c>
+      <c r="H248" t="s">
         <v>25</v>
       </c>
-      <c r="I248" s="35" t="s">
+      <c r="I248" t="s">
         <v>12</v>
       </c>
-      <c r="J248" s="35" t="s">
+      <c r="J248" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="250" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="251" spans="1:10" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>368</v>
+      </c>
+      <c r="B249" s="4">
+        <v>46027</v>
+      </c>
+      <c r="C249" t="s">
+        <v>20</v>
+      </c>
+      <c r="D249" t="s">
+        <v>209</v>
+      </c>
+      <c r="E249" t="s">
+        <v>498</v>
+      </c>
+      <c r="F249" t="s">
+        <v>499</v>
+      </c>
+      <c r="G249" t="s">
+        <v>10</v>
+      </c>
+      <c r="H249" t="s">
+        <v>60</v>
+      </c>
+      <c r="I249" t="s">
+        <v>501</v>
+      </c>
+      <c r="J249" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>368</v>
+      </c>
+      <c r="B250" s="4">
+        <v>46027</v>
+      </c>
+      <c r="C250" t="s">
+        <v>20</v>
+      </c>
+      <c r="D250" t="s">
+        <v>209</v>
+      </c>
+      <c r="E250" t="s">
+        <v>209</v>
+      </c>
+      <c r="F250" t="s">
+        <v>500</v>
+      </c>
+      <c r="G250" t="s">
+        <v>10</v>
+      </c>
+      <c r="H250" t="s">
+        <v>203</v>
+      </c>
+      <c r="I250" t="s">
+        <v>501</v>
+      </c>
+      <c r="J250" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>369</v>
+      </c>
+      <c r="B251" s="4">
+        <v>46028</v>
+      </c>
+      <c r="C251" t="s">
+        <v>43</v>
+      </c>
+      <c r="D251" t="s">
+        <v>254</v>
+      </c>
+      <c r="E251" t="s">
+        <v>48</v>
+      </c>
+      <c r="F251" t="s">
+        <v>471</v>
+      </c>
+      <c r="G251" t="s">
+        <v>10</v>
+      </c>
+      <c r="H251" t="s">
+        <v>45</v>
+      </c>
+      <c r="I251" t="s">
+        <v>502</v>
+      </c>
+      <c r="J251" t="s">
+        <v>505</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:J251" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="9">
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <filters>
-            <x14:filter val="Se reinicia plc en PLL-02, ya que no actualizaba datos. _x000a__x000a_Se agrega marca de reseteo en ecostruxture (M801) para que termine de contar y reinicie el ciclo. _x000a__x000a_Sonda y caudalimetro funciona correctamente. _x000a__x000a_Se solicita a operador tranque activar el pozo para realizar medición de caudal, resultando correcta la validación del dato en terreno con lo mostrado en plataforma._x000a__x000a_Se actualiza en plataforma los valores del volumen en el punto asique mostrará un peak aprox a las 17:00hrs."/>
-          </filters>
-        </mc:Choice>
-        <mc:Fallback>
-          <customFilters>
-            <customFilter val=""/>
-            <customFilter operator="notEqual" val=" "/>
-          </customFilters>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J251">
-      <sortCondition ref="A1:A251"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -18631,7 +16803,7 @@
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="19">
         <v>16</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -18669,37 +16841,37 @@
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="19">
         <v>92</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="26">
         <v>9</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="26">
         <v>12</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="26">
         <v>11</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="26">
         <v>23</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="26">
         <v>13</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="26">
         <v>90</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="26">
         <v>13</v>
       </c>
-      <c r="N5" s="24">
+      <c r="N5" s="26">
         <v>1</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="30">
         <v>172</v>
       </c>
     </row>
@@ -18707,35 +16879,35 @@
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="19">
         <v>40</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="31">
         <v>4</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="31">
         <v>8</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="31">
         <v>5</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="31">
         <v>1</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="31">
         <v>11</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="31">
         <v>1</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="31">
         <v>2</v>
       </c>
-      <c r="N6" s="26"/>
-      <c r="O6" s="27">
+      <c r="N6" s="31"/>
+      <c r="O6" s="32">
         <v>32</v>
       </c>
     </row>
@@ -18743,31 +16915,31 @@
       <c r="A7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <v>29</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="33">
         <v>5</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="33">
         <v>3</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>5</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="33">
         <v>5</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="33">
         <v>7</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="31">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="34">
         <v>25</v>
       </c>
     </row>
@@ -18775,23 +16947,23 @@
       <c r="A8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <v>22</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18">
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20">
         <v>1</v>
       </c>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="22">
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="24">
         <v>1</v>
       </c>
     </row>
@@ -18799,25 +16971,25 @@
       <c r="A9" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18">
+      <c r="G9" s="20"/>
+      <c r="H9" s="20">
         <v>1</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18">
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20">
         <v>1</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="22">
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="24">
         <v>2</v>
       </c>
     </row>
@@ -18825,23 +16997,23 @@
       <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="19">
         <v>28</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18">
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20">
         <v>1</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="22">
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="24">
         <v>1</v>
       </c>
     </row>
@@ -18849,23 +17021,23 @@
       <c r="A11" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="19">
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18">
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20">
         <v>1</v>
       </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="22">
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="24">
         <v>1</v>
       </c>
     </row>
@@ -18873,27 +17045,27 @@
       <c r="A12" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="19">
         <v>247</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18">
+      <c r="G12" s="20"/>
+      <c r="H12" s="20">
         <v>2</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18">
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20">
         <v>1</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18">
+      <c r="L12" s="20"/>
+      <c r="M12" s="20">
         <v>1</v>
       </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="22">
+      <c r="N12" s="20"/>
+      <c r="O12" s="24">
         <v>4</v>
       </c>
     </row>
@@ -18901,19 +17073,19 @@
       <c r="F13" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18">
+      <c r="G13" s="20"/>
+      <c r="H13" s="20">
         <v>1</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18">
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20">
         <v>2</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="22">
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="24">
         <v>3</v>
       </c>
     </row>
@@ -18921,21 +17093,21 @@
       <c r="F14" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18">
+      <c r="G14" s="20"/>
+      <c r="H14" s="20">
         <v>1</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="20">
         <v>1</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18">
+      <c r="J14" s="20"/>
+      <c r="K14" s="20">
         <v>1</v>
       </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="22">
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="24">
         <v>3</v>
       </c>
     </row>
@@ -18943,17 +17115,17 @@
       <c r="F15" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18">
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20">
         <v>2</v>
       </c>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="22">
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="24">
         <v>2</v>
       </c>
     </row>
@@ -18961,17 +17133,17 @@
       <c r="F16" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="20">
         <v>1</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="22">
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="24">
         <v>1</v>
       </c>
     </row>
@@ -18979,31 +17151,31 @@
       <c r="F17" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="21">
         <v>19</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="22">
         <v>28</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="22">
         <v>22</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="22">
         <v>29</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="22">
         <v>40</v>
       </c>
-      <c r="L17" s="20">
+      <c r="L17" s="22">
         <v>92</v>
       </c>
-      <c r="M17" s="20">
+      <c r="M17" s="22">
         <v>16</v>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="22">
         <v>1</v>
       </c>
-      <c r="O17" s="23">
+      <c r="O17" s="25">
         <v>247</v>
       </c>
     </row>
@@ -19059,25 +17231,25 @@
       <c r="F24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18">
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20">
         <v>2</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="20">
         <v>3</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="20">
         <v>4</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="20">
         <v>3</v>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="20">
         <v>1</v>
       </c>
-      <c r="N24" s="18"/>
-      <c r="O24" s="21">
+      <c r="N24" s="20"/>
+      <c r="O24" s="23">
         <v>13</v>
       </c>
     </row>
@@ -19113,19 +17285,19 @@
       <c r="F26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18">
+      <c r="G26" s="20"/>
+      <c r="H26" s="20">
         <v>3</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18">
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20">
         <v>7</v>
       </c>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="22">
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="24">
         <v>10</v>
       </c>
     </row>
@@ -19133,27 +17305,27 @@
       <c r="F27" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="20">
         <v>3</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="20">
         <v>1</v>
       </c>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18">
+      <c r="I27" s="20"/>
+      <c r="J27" s="20">
         <v>4</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="20">
         <v>2</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="20">
         <v>5</v>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="20">
         <v>8</v>
       </c>
-      <c r="N27" s="18"/>
-      <c r="O27" s="22">
+      <c r="N27" s="20"/>
+      <c r="O27" s="24">
         <v>23</v>
       </c>
     </row>
@@ -19191,19 +17363,19 @@
       <c r="F29" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18">
+      <c r="G29" s="20"/>
+      <c r="H29" s="20">
         <v>2</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="20">
         <v>1</v>
       </c>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="22">
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="24">
         <v>3</v>
       </c>
     </row>
@@ -19211,21 +17383,21 @@
       <c r="F30" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="20">
         <v>3</v>
       </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18">
+      <c r="H30" s="20"/>
+      <c r="I30" s="20">
         <v>2</v>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="20">
         <v>1</v>
       </c>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="22">
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19233,31 +17405,31 @@
       <c r="F31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="26">
         <v>3</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="26">
         <v>1</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="26">
         <v>9</v>
       </c>
-      <c r="J31" s="24">
+      <c r="J31" s="26">
         <v>14</v>
       </c>
-      <c r="K31" s="24">
+      <c r="K31" s="26">
         <v>7</v>
       </c>
-      <c r="L31" s="24">
+      <c r="L31" s="26">
         <v>67</v>
       </c>
-      <c r="M31" s="24">
+      <c r="M31" s="26">
         <v>3</v>
       </c>
-      <c r="N31" s="24">
+      <c r="N31" s="26">
         <v>1</v>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="27">
         <v>105</v>
       </c>
     </row>
@@ -19265,17 +17437,17 @@
       <c r="F32" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18">
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20">
         <v>1</v>
       </c>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="22">
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="24">
         <v>1</v>
       </c>
     </row>
@@ -19283,17 +17455,17 @@
       <c r="F33" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18">
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20">
         <v>1</v>
       </c>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="22">
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="24">
         <v>1</v>
       </c>
       <c r="AH33" t="s">
@@ -19304,31 +17476,31 @@
       <c r="F34" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="21">
         <v>19</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="22">
         <v>28</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="22">
         <v>22</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="22">
         <v>29</v>
       </c>
-      <c r="K34" s="20">
+      <c r="K34" s="22">
         <v>40</v>
       </c>
-      <c r="L34" s="20">
+      <c r="L34" s="22">
         <v>92</v>
       </c>
-      <c r="M34" s="20">
+      <c r="M34" s="22">
         <v>16</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="22">
         <v>1</v>
       </c>
-      <c r="O34" s="23">
+      <c r="O34" s="25">
         <v>247</v>
       </c>
     </row>

--- a/reasignacion_st_detallada.xlsx
+++ b/reasignacion_st_detallada.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3D8183-6C8C-9D4D-AB41-DB3762BAD205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DC27CE-7679-D841-934A-F95030D3540E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="600" windowWidth="29420" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33600" yWindow="-5560" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reclasifiación ST" sheetId="1" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'reclasifiación ST'!$A$1:$J$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'reclasifiación ST'!$A$1:$J$260</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="270" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="522">
   <si>
     <t>OT</t>
   </si>
@@ -1873,6 +1873,72 @@
     <t>Se intstala sensor de nivel en pozo y se configura el equipo junto con el flujometro a traves de lecturas modbus, se comprueban valores en PLC.
 Por otro lado se configura la comunicación del punto a la telemetria WeTechs para la visualizacion de datos.
 Adicionalmente se instalan equipos de comunicación para la lectura de datos a través de red LORA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Válvula desde piscina UG hacia piscina 3800 </t>
+  </si>
+  <si>
+    <t>Se acude al punto para cerrar válvula por completo por solicitud del cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude al punto para resolución de ticket, ya que presentaba peaks de valores respecto a la conductividaddel agua en plataforma.
+Se revisan software y se verifica la lectura
+Se encuentra en orden y registrando valores en plataforma. </t>
+  </si>
+  <si>
+    <t>Mantenimiento correctivo R2700</t>
+  </si>
+  <si>
+    <t>Implementacion red LORA WAN</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN4</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo O4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planta Solar </t>
+  </si>
+  <si>
+    <t>[APR Los Caleos] Pozo 4</t>
+  </si>
+  <si>
+    <t>En la visita a terreno se constata que la caida de la telemetria se debe a la desnergizacion de antena starlink, esto ultimo por activación de interruptor automático.
+Se regulariza la condición y adicionalmente se integra la UPS al circuito de alimentación conectando entrada en tablero de paso existente y su salida aguas arriba a automático general telemetría. 
+De esta forma si la red electerica cae, la UPS continuará entregandole energia al sistema completo, una vez la UPS se agote, el inversor continua alimentando con baterias y solución solar.
+Queda pendiente en sala R2700 instalar gabinete para remontar 2 baterias de 100AH y conectarlas al sistema de respaldo.
+Instalación de conectores MC4 paralelo para regularizar la conexión fisica de los paneles.
+Instalar automático DC para la protección de banco de baterías.
+Regularizar terminales en cables de alimentación solar y baterías (requiere ferrules) cable 6AWG.</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado.</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisión de los pozos de inyección del 17 al 20.
+Se contrasta Caudal en terreno y en plataforma siendo estos 4 puntos coherentes y valores correctos
+Se revisa planta Solar y se limpian paneles para evitar algún tipo de falla respectivamente.
+Observaciones
+PI-17 se destraba válvula vortex y continua su funcionamiento normal.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisar el pozo 4 de los caleos por la falla que tuvo el día de ayer, hablamos con el operador y comento que hoy le paso algo parecido y volvió la señal, también hace unas semanas en un turno de noche como 3 veces. Asique fuimos al punto con el para ver la situación 
+- Tablero We connect presenta muy alta temperatura en teltonika y en el tablero en general, tablero no cuenta con ventilación 
+- Fuente de voltaje estaba en 28,40v se reduce a 26,20, por sobrecalentamiento, se observa que potenciómetro de voltaje de la fuente esta hundido hacia dentro y se hace difícil regular.
+Son indicios para pensar en reemplazar la fuente y quizás una mejora en sentido de ventilación o enfriamiento del tablero. </t>
+  </si>
+  <si>
+    <t>(Todas)</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1968,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1936,6 +2002,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2053,7 +2125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2114,6 +2186,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2133,190 +2208,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="104">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="116">
     <dxf>
       <border>
         <left style="thin">
@@ -2451,6 +2343,20 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2606,6 +2512,185 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -2745,6 +2830,34 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -2878,6 +2991,20 @@
           <color indexed="64"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3028,6 +3155,38 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -4734,7 +4893,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daniel Cuero" refreshedDate="46029.494483796298" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="247" xr:uid="{0361626B-1122-CE47-8D2B-862A439D0806}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Daniel Cuero" refreshedDate="46031.457185995372" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="247" xr:uid="{0361626B-1122-CE47-8D2B-862A439D0806}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J248" sheet="reclasifiación ST"/>
   </cacheSource>
@@ -4743,7 +4902,82 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="78" maxValue="365"/>
     </cacheField>
     <cacheField name="Fecha" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-08-25T00:00:00" maxDate="2026-01-01T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-08-25T00:00:00" maxDate="2026-01-01T00:00:00" count="74">
+        <d v="2025-08-25T00:00:00"/>
+        <d v="2025-08-27T00:00:00"/>
+        <d v="2025-09-02T00:00:00"/>
+        <d v="2025-09-03T00:00:00"/>
+        <d v="2025-09-05T00:00:00"/>
+        <d v="2025-09-06T00:00:00"/>
+        <d v="2025-09-08T00:00:00"/>
+        <d v="2025-09-04T00:00:00"/>
+        <d v="2025-09-10T00:00:00"/>
+        <d v="2025-09-12T00:00:00"/>
+        <d v="2025-09-13T00:00:00"/>
+        <d v="2025-09-16T00:00:00"/>
+        <d v="2025-09-23T00:00:00"/>
+        <d v="2025-09-24T00:00:00"/>
+        <d v="2025-09-25T00:00:00"/>
+        <d v="2025-09-27T00:00:00"/>
+        <d v="2025-09-30T00:00:00"/>
+        <d v="2025-10-02T00:00:00"/>
+        <d v="2025-10-03T00:00:00"/>
+        <d v="2025-10-07T00:00:00"/>
+        <d v="2025-10-08T00:00:00"/>
+        <d v="2025-10-09T00:00:00"/>
+        <d v="2025-10-10T00:00:00"/>
+        <d v="2025-10-11T00:00:00"/>
+        <d v="2025-10-13T00:00:00"/>
+        <d v="2025-10-14T00:00:00"/>
+        <d v="2025-10-15T00:00:00"/>
+        <d v="2025-10-16T00:00:00"/>
+        <d v="2025-10-17T00:00:00"/>
+        <d v="2025-10-21T00:00:00"/>
+        <d v="2025-10-22T00:00:00"/>
+        <d v="2025-10-23T00:00:00"/>
+        <d v="2025-10-27T00:00:00"/>
+        <d v="2025-10-28T00:00:00"/>
+        <d v="2025-10-30T00:00:00"/>
+        <d v="2025-11-04T00:00:00"/>
+        <d v="2025-11-05T00:00:00"/>
+        <d v="2025-11-06T00:00:00"/>
+        <d v="2025-11-07T00:00:00"/>
+        <d v="2025-11-10T00:00:00"/>
+        <d v="2025-11-11T00:00:00"/>
+        <d v="2025-11-12T00:00:00"/>
+        <d v="2025-11-13T00:00:00"/>
+        <d v="2025-11-14T00:00:00"/>
+        <d v="2025-11-17T00:00:00"/>
+        <d v="2025-11-18T00:00:00"/>
+        <d v="2025-11-19T00:00:00"/>
+        <d v="2025-11-21T00:00:00"/>
+        <d v="2025-11-24T00:00:00"/>
+        <d v="2025-11-25T00:00:00"/>
+        <d v="2025-11-26T00:00:00"/>
+        <d v="2025-11-27T00:00:00"/>
+        <d v="2025-11-28T00:00:00"/>
+        <d v="2025-12-01T00:00:00"/>
+        <d v="2025-12-02T00:00:00"/>
+        <d v="2025-12-03T00:00:00"/>
+        <d v="2025-12-04T00:00:00"/>
+        <d v="2025-12-05T00:00:00"/>
+        <d v="2025-12-10T00:00:00"/>
+        <d v="2025-12-09T00:00:00"/>
+        <d v="2025-12-11T00:00:00"/>
+        <d v="2025-12-15T00:00:00"/>
+        <d v="2025-12-16T00:00:00"/>
+        <d v="2025-12-17T00:00:00"/>
+        <d v="2025-12-18T00:00:00"/>
+        <d v="2025-12-19T00:00:00"/>
+        <d v="2025-12-23T00:00:00"/>
+        <d v="2025-12-22T00:00:00"/>
+        <d v="2025-12-25T00:00:00"/>
+        <d v="2025-12-26T00:00:00"/>
+        <d v="2025-12-24T00:00:00"/>
+        <d v="2025-12-29T00:00:00"/>
+        <d v="2025-12-30T00:00:00"/>
+        <d v="2025-12-31T00:00:00"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Técnico" numFmtId="0">
       <sharedItems containsBlank="1" count="11">
@@ -4818,7 +5052,7 @@
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="247">
   <r>
     <n v="78"/>
-    <d v="2025-08-25T00:00:00"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <s v="ASP Pozos"/>
@@ -4830,7 +5064,7 @@
   </r>
   <r>
     <n v="81"/>
-    <d v="2025-08-25T00:00:00"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4842,7 +5076,7 @@
   </r>
   <r>
     <n v="81"/>
-    <d v="2025-08-25T00:00:00"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4854,7 +5088,7 @@
   </r>
   <r>
     <n v="83"/>
-    <d v="2025-08-27T00:00:00"/>
+    <x v="1"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4866,7 +5100,7 @@
   </r>
   <r>
     <n v="93"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4878,7 +5112,7 @@
   </r>
   <r>
     <n v="93"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4890,7 +5124,7 @@
   </r>
   <r>
     <n v="94"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -4902,7 +5136,7 @@
   </r>
   <r>
     <n v="94"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -4914,7 +5148,7 @@
   </r>
   <r>
     <n v="94"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -4926,7 +5160,7 @@
   </r>
   <r>
     <n v="94"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -4938,7 +5172,7 @@
   </r>
   <r>
     <n v="95"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -4950,7 +5184,7 @@
   </r>
   <r>
     <n v="96"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -4962,7 +5196,7 @@
   </r>
   <r>
     <n v="97"/>
-    <d v="2025-09-02T00:00:00"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4974,7 +5208,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -4986,7 +5220,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
     <s v="El Soldado Cachimba Relevadoras"/>
@@ -4998,7 +5232,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
     <s v="El Soldado Cachimba El Cobre"/>
@@ -5010,7 +5244,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5022,7 +5256,7 @@
   </r>
   <r>
     <n v="101"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5034,7 +5268,7 @@
   </r>
   <r>
     <n v="105"/>
-    <d v="2025-09-05T00:00:00"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5046,7 +5280,7 @@
   </r>
   <r>
     <n v="105"/>
-    <d v="2025-09-05T00:00:00"/>
+    <x v="4"/>
     <x v="4"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5058,7 +5292,7 @@
   </r>
   <r>
     <n v="110"/>
-    <d v="2025-09-06T00:00:00"/>
+    <x v="5"/>
     <x v="4"/>
     <x v="4"/>
     <s v="Abastible - PSR La Estrella"/>
@@ -5070,7 +5304,7 @@
   </r>
   <r>
     <n v="110"/>
-    <d v="2025-09-06T00:00:00"/>
+    <x v="5"/>
     <x v="4"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5082,7 +5316,7 @@
   </r>
   <r>
     <n v="110"/>
-    <d v="2025-09-06T00:00:00"/>
+    <x v="5"/>
     <x v="4"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5094,7 +5328,7 @@
   </r>
   <r>
     <n v="111"/>
-    <d v="2025-09-08T00:00:00"/>
+    <x v="6"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5106,7 +5340,7 @@
   </r>
   <r>
     <n v="111"/>
-    <d v="2025-09-08T00:00:00"/>
+    <x v="6"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5118,7 +5352,7 @@
   </r>
   <r>
     <n v="111"/>
-    <d v="2025-09-08T00:00:00"/>
+    <x v="6"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5130,7 +5364,7 @@
   </r>
   <r>
     <n v="114"/>
-    <d v="2025-09-04T00:00:00"/>
+    <x v="7"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5142,7 +5376,7 @@
   </r>
   <r>
     <n v="114"/>
-    <d v="2025-09-04T00:00:00"/>
+    <x v="7"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5154,7 +5388,7 @@
   </r>
   <r>
     <n v="115"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5166,7 +5400,7 @@
   </r>
   <r>
     <n v="115"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5178,7 +5412,7 @@
   </r>
   <r>
     <n v="115"/>
-    <d v="2025-09-03T00:00:00"/>
+    <x v="3"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5190,7 +5424,7 @@
   </r>
   <r>
     <n v="117"/>
-    <d v="2025-09-10T00:00:00"/>
+    <x v="8"/>
     <x v="1"/>
     <x v="3"/>
     <s v="SMA res 31 "/>
@@ -5202,7 +5436,7 @@
   </r>
   <r>
     <n v="118"/>
-    <d v="2025-09-10T00:00:00"/>
+    <x v="8"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5214,7 +5448,7 @@
   </r>
   <r>
     <n v="118"/>
-    <d v="2025-09-10T00:00:00"/>
+    <x v="8"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5226,7 +5460,7 @@
   </r>
   <r>
     <n v="119"/>
-    <d v="2025-09-10T00:00:00"/>
+    <x v="8"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5238,7 +5472,7 @@
   </r>
   <r>
     <n v="123"/>
-    <d v="2025-09-12T00:00:00"/>
+    <x v="9"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5250,7 +5484,7 @@
   </r>
   <r>
     <n v="123"/>
-    <d v="2025-09-12T00:00:00"/>
+    <x v="9"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5262,7 +5496,7 @@
   </r>
   <r>
     <n v="126"/>
-    <d v="2025-09-13T00:00:00"/>
+    <x v="10"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5274,7 +5508,7 @@
   </r>
   <r>
     <n v="126"/>
-    <d v="2025-09-13T00:00:00"/>
+    <x v="10"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5286,7 +5520,7 @@
   </r>
   <r>
     <n v="130"/>
-    <d v="2025-09-16T00:00:00"/>
+    <x v="11"/>
     <x v="0"/>
     <x v="5"/>
     <s v="Viñas de Chicureo"/>
@@ -5298,7 +5532,7 @@
   </r>
   <r>
     <n v="130"/>
-    <d v="2025-09-16T00:00:00"/>
+    <x v="11"/>
     <x v="0"/>
     <x v="5"/>
     <s v="Viñas de Chicureo"/>
@@ -5310,7 +5544,7 @@
   </r>
   <r>
     <n v="132"/>
-    <d v="2025-09-16T00:00:00"/>
+    <x v="11"/>
     <x v="6"/>
     <x v="6"/>
     <s v="Estadio Español"/>
@@ -5322,7 +5556,7 @@
   </r>
   <r>
     <n v="143"/>
-    <d v="2025-09-23T00:00:00"/>
+    <x v="12"/>
     <x v="0"/>
     <x v="7"/>
     <s v="Brisaguas - La Cruz"/>
@@ -5334,7 +5568,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5346,7 +5580,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5358,7 +5592,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado Reforestacion"/>
@@ -5370,7 +5604,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5382,7 +5616,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5394,7 +5628,7 @@
   </r>
   <r>
     <n v="148"/>
-    <d v="2025-09-24T00:00:00"/>
+    <x v="13"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5406,7 +5640,7 @@
   </r>
   <r>
     <n v="153"/>
-    <d v="2025-09-25T00:00:00"/>
+    <x v="14"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5418,7 +5652,7 @@
   </r>
   <r>
     <n v="153"/>
-    <d v="2025-09-25T00:00:00"/>
+    <x v="14"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5430,7 +5664,7 @@
   </r>
   <r>
     <n v="153"/>
-    <d v="2025-09-25T00:00:00"/>
+    <x v="14"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5442,7 +5676,7 @@
   </r>
   <r>
     <n v="155"/>
-    <d v="2025-09-27T00:00:00"/>
+    <x v="15"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5454,7 +5688,7 @@
   </r>
   <r>
     <n v="163"/>
-    <d v="2025-09-30T00:00:00"/>
+    <x v="16"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5466,7 +5700,7 @@
   </r>
   <r>
     <n v="163"/>
-    <d v="2025-09-30T00:00:00"/>
+    <x v="16"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5478,7 +5712,7 @@
   </r>
   <r>
     <n v="163"/>
-    <d v="2025-09-30T00:00:00"/>
+    <x v="16"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5490,7 +5724,7 @@
   </r>
   <r>
     <n v="164"/>
-    <d v="2025-09-30T00:00:00"/>
+    <x v="16"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -5502,7 +5736,7 @@
   </r>
   <r>
     <n v="166"/>
-    <d v="2025-10-02T00:00:00"/>
+    <x v="17"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5514,7 +5748,7 @@
   </r>
   <r>
     <n v="168"/>
-    <d v="2025-10-02T00:00:00"/>
+    <x v="17"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5526,7 +5760,7 @@
   </r>
   <r>
     <n v="172"/>
-    <d v="2025-10-02T00:00:00"/>
+    <x v="17"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5538,7 +5772,7 @@
   </r>
   <r>
     <n v="172"/>
-    <d v="2025-10-02T00:00:00"/>
+    <x v="17"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5550,7 +5784,7 @@
   </r>
   <r>
     <n v="172"/>
-    <d v="2025-10-02T00:00:00"/>
+    <x v="17"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5562,7 +5796,7 @@
   </r>
   <r>
     <n v="175"/>
-    <d v="2025-10-03T00:00:00"/>
+    <x v="18"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5574,7 +5808,7 @@
   </r>
   <r>
     <n v="175"/>
-    <d v="2025-10-03T00:00:00"/>
+    <x v="18"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5586,7 +5820,7 @@
   </r>
   <r>
     <n v="175"/>
-    <d v="2025-10-03T00:00:00"/>
+    <x v="18"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5598,7 +5832,7 @@
   </r>
   <r>
     <n v="175"/>
-    <d v="2025-10-03T00:00:00"/>
+    <x v="18"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5610,7 +5844,7 @@
   </r>
   <r>
     <n v="176"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5622,7 +5856,7 @@
   </r>
   <r>
     <n v="176"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5634,7 +5868,7 @@
   </r>
   <r>
     <n v="176"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5646,7 +5880,7 @@
   </r>
   <r>
     <n v="179"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="0"/>
     <x v="8"/>
     <s v="SSR Comité Manzanar"/>
@@ -5658,7 +5892,7 @@
   </r>
   <r>
     <n v="180"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="0"/>
     <x v="9"/>
     <s v="APR Parcelación El Melón RP1"/>
@@ -5670,7 +5904,7 @@
   </r>
   <r>
     <n v="182"/>
-    <d v="2025-10-07T00:00:00"/>
+    <x v="19"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5682,7 +5916,7 @@
   </r>
   <r>
     <n v="183"/>
-    <d v="2025-10-08T00:00:00"/>
+    <x v="20"/>
     <x v="0"/>
     <x v="10"/>
     <s v="Lipigas PSR Quillayes"/>
@@ -5694,7 +5928,7 @@
   </r>
   <r>
     <n v="187"/>
-    <d v="2025-10-09T00:00:00"/>
+    <x v="21"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5706,7 +5940,7 @@
   </r>
   <r>
     <n v="187"/>
-    <d v="2025-10-09T00:00:00"/>
+    <x v="21"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5718,7 +5952,7 @@
   </r>
   <r>
     <n v="187"/>
-    <d v="2025-10-09T00:00:00"/>
+    <x v="21"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5730,7 +5964,7 @@
   </r>
   <r>
     <n v="187"/>
-    <d v="2025-10-09T00:00:00"/>
+    <x v="21"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5742,7 +5976,7 @@
   </r>
   <r>
     <n v="190"/>
-    <d v="2025-10-09T00:00:00"/>
+    <x v="21"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5754,7 +5988,7 @@
   </r>
   <r>
     <n v="191"/>
-    <d v="2025-10-10T00:00:00"/>
+    <x v="22"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5766,7 +6000,7 @@
   </r>
   <r>
     <n v="191"/>
-    <d v="2025-10-10T00:00:00"/>
+    <x v="22"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5778,7 +6012,7 @@
   </r>
   <r>
     <n v="191"/>
-    <d v="2025-10-10T00:00:00"/>
+    <x v="22"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5790,7 +6024,7 @@
   </r>
   <r>
     <n v="191"/>
-    <d v="2025-10-10T00:00:00"/>
+    <x v="22"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5802,7 +6036,7 @@
   </r>
   <r>
     <n v="192"/>
-    <d v="2025-10-11T00:00:00"/>
+    <x v="23"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5814,7 +6048,7 @@
   </r>
   <r>
     <n v="194"/>
-    <d v="2025-10-13T00:00:00"/>
+    <x v="24"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5826,7 +6060,7 @@
   </r>
   <r>
     <n v="196"/>
-    <d v="2025-10-14T00:00:00"/>
+    <x v="25"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -5838,7 +6072,7 @@
   </r>
   <r>
     <n v="196"/>
-    <d v="2025-10-14T00:00:00"/>
+    <x v="25"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Resolucion 31 calidad de aguas "/>
@@ -5850,7 +6084,7 @@
   </r>
   <r>
     <n v="196"/>
-    <d v="2025-10-14T00:00:00"/>
+    <x v="25"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Resolución 31 monitoreo calidad de aguas "/>
@@ -5862,7 +6096,7 @@
   </r>
   <r>
     <n v="196"/>
-    <d v="2025-10-14T00:00:00"/>
+    <x v="25"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Resolución 31 monitoreo y calidad de aguas "/>
@@ -5874,7 +6108,7 @@
   </r>
   <r>
     <n v="199"/>
-    <d v="2025-10-15T00:00:00"/>
+    <x v="26"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5886,7 +6120,7 @@
   </r>
   <r>
     <n v="202"/>
-    <d v="2025-10-15T00:00:00"/>
+    <x v="26"/>
     <x v="7"/>
     <x v="3"/>
     <s v="Resolución 31 monitoreo y calidad de aguas "/>
@@ -5898,7 +6132,7 @@
   </r>
   <r>
     <n v="205"/>
-    <d v="2025-10-16T00:00:00"/>
+    <x v="27"/>
     <x v="2"/>
     <x v="1"/>
     <s v="El Soldado Cachimba Relevadoras"/>
@@ -5910,7 +6144,7 @@
   </r>
   <r>
     <n v="206"/>
-    <d v="2025-10-16T00:00:00"/>
+    <x v="27"/>
     <x v="0"/>
     <x v="10"/>
     <s v="Sala de control GNL Lipigas "/>
@@ -5922,7 +6156,7 @@
   </r>
   <r>
     <n v="213"/>
-    <d v="2025-10-17T00:00:00"/>
+    <x v="28"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5934,7 +6168,7 @@
   </r>
   <r>
     <n v="214"/>
-    <d v="2025-10-17T00:00:00"/>
+    <x v="28"/>
     <x v="0"/>
     <x v="10"/>
     <s v="Lipigas PSR Danone (Chillán)"/>
@@ -5946,7 +6180,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5958,7 +6192,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5970,7 +6204,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5982,7 +6216,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -5994,7 +6228,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6006,7 +6240,7 @@
   </r>
   <r>
     <n v="217"/>
-    <d v="2025-10-21T00:00:00"/>
+    <x v="29"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6018,7 +6252,7 @@
   </r>
   <r>
     <n v="219"/>
-    <d v="2025-10-22T00:00:00"/>
+    <x v="30"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6030,7 +6264,7 @@
   </r>
   <r>
     <n v="219"/>
-    <d v="2025-10-22T00:00:00"/>
+    <x v="30"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6042,7 +6276,7 @@
   </r>
   <r>
     <n v="219"/>
-    <d v="2025-10-22T00:00:00"/>
+    <x v="30"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6054,7 +6288,7 @@
   </r>
   <r>
     <n v="219"/>
-    <d v="2025-10-22T00:00:00"/>
+    <x v="30"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6066,7 +6300,7 @@
   </r>
   <r>
     <n v="223"/>
-    <d v="2025-10-23T00:00:00"/>
+    <x v="31"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6078,7 +6312,7 @@
   </r>
   <r>
     <n v="223"/>
-    <d v="2025-10-23T00:00:00"/>
+    <x v="31"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6090,7 +6324,7 @@
   </r>
   <r>
     <n v="223"/>
-    <d v="2025-10-23T00:00:00"/>
+    <x v="31"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6102,7 +6336,7 @@
   </r>
   <r>
     <n v="223"/>
-    <d v="2025-10-23T00:00:00"/>
+    <x v="31"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6114,7 +6348,7 @@
   </r>
   <r>
     <n v="231"/>
-    <d v="2025-10-27T00:00:00"/>
+    <x v="32"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6126,7 +6360,7 @@
   </r>
   <r>
     <n v="233"/>
-    <d v="2025-10-27T00:00:00"/>
+    <x v="32"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6138,7 +6372,7 @@
   </r>
   <r>
     <n v="233"/>
-    <d v="2025-10-27T00:00:00"/>
+    <x v="32"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6150,7 +6384,7 @@
   </r>
   <r>
     <n v="233"/>
-    <d v="2025-10-27T00:00:00"/>
+    <x v="32"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6162,7 +6396,7 @@
   </r>
   <r>
     <n v="233"/>
-    <d v="2025-10-27T00:00:00"/>
+    <x v="32"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6174,7 +6408,7 @@
   </r>
   <r>
     <n v="234"/>
-    <d v="2025-10-28T00:00:00"/>
+    <x v="33"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6186,7 +6420,7 @@
   </r>
   <r>
     <n v="236"/>
-    <d v="2025-10-28T00:00:00"/>
+    <x v="33"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6198,7 +6432,7 @@
   </r>
   <r>
     <n v="236"/>
-    <d v="2025-10-28T00:00:00"/>
+    <x v="33"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6210,7 +6444,7 @@
   </r>
   <r>
     <n v="240"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6222,7 +6456,7 @@
   </r>
   <r>
     <n v="240"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6234,7 +6468,7 @@
   </r>
   <r>
     <n v="242"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6246,7 +6480,7 @@
   </r>
   <r>
     <n v="242"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6258,7 +6492,7 @@
   </r>
   <r>
     <n v="242"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6270,7 +6504,7 @@
   </r>
   <r>
     <n v="242"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6282,7 +6516,7 @@
   </r>
   <r>
     <n v="242"/>
-    <d v="2025-10-30T00:00:00"/>
+    <x v="34"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6294,7 +6528,7 @@
   </r>
   <r>
     <n v="244"/>
-    <d v="2025-11-04T00:00:00"/>
+    <x v="35"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Recursos Hidricos el soldado "/>
@@ -6306,7 +6540,7 @@
   </r>
   <r>
     <n v="244"/>
-    <d v="2025-11-04T00:00:00"/>
+    <x v="35"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6318,7 +6552,7 @@
   </r>
   <r>
     <n v="246"/>
-    <d v="2025-11-05T00:00:00"/>
+    <x v="36"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Recursos Hidricos el soldado "/>
@@ -6330,7 +6564,7 @@
   </r>
   <r>
     <n v="246"/>
-    <d v="2025-11-05T00:00:00"/>
+    <x v="36"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6342,7 +6576,7 @@
   </r>
   <r>
     <n v="249"/>
-    <d v="2025-11-06T00:00:00"/>
+    <x v="37"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Recursos Hidricos el soldado "/>
@@ -6354,7 +6588,7 @@
   </r>
   <r>
     <n v="253"/>
-    <d v="2025-11-06T00:00:00"/>
+    <x v="37"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -6366,7 +6600,7 @@
   </r>
   <r>
     <n v="253"/>
-    <d v="2025-11-06T00:00:00"/>
+    <x v="37"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6378,7 +6612,7 @@
   </r>
   <r>
     <n v="254"/>
-    <d v="2025-11-07T00:00:00"/>
+    <x v="38"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6390,7 +6624,7 @@
   </r>
   <r>
     <n v="255"/>
-    <d v="2025-11-07T00:00:00"/>
+    <x v="38"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6402,7 +6636,7 @@
   </r>
   <r>
     <n v="255"/>
-    <d v="2025-11-07T00:00:00"/>
+    <x v="38"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6414,7 +6648,7 @@
   </r>
   <r>
     <n v="258"/>
-    <d v="2025-11-10T00:00:00"/>
+    <x v="39"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6426,7 +6660,7 @@
   </r>
   <r>
     <n v="258"/>
-    <d v="2025-11-10T00:00:00"/>
+    <x v="39"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6438,7 +6672,7 @@
   </r>
   <r>
     <n v="260"/>
-    <d v="2025-11-11T00:00:00"/>
+    <x v="40"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6450,7 +6684,7 @@
   </r>
   <r>
     <n v="262"/>
-    <d v="2025-11-12T00:00:00"/>
+    <x v="41"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6462,7 +6696,7 @@
   </r>
   <r>
     <n v="262"/>
-    <d v="2025-11-12T00:00:00"/>
+    <x v="41"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -6474,7 +6708,7 @@
   </r>
   <r>
     <n v="266"/>
-    <d v="2025-11-13T00:00:00"/>
+    <x v="42"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6486,7 +6720,7 @@
   </r>
   <r>
     <n v="266"/>
-    <d v="2025-11-13T00:00:00"/>
+    <x v="42"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6498,7 +6732,7 @@
   </r>
   <r>
     <n v="266"/>
-    <d v="2025-11-13T00:00:00"/>
+    <x v="42"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6510,7 +6744,7 @@
   </r>
   <r>
     <n v="266"/>
-    <d v="2025-11-13T00:00:00"/>
+    <x v="42"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6522,7 +6756,7 @@
   </r>
   <r>
     <n v="267"/>
-    <d v="2025-11-14T00:00:00"/>
+    <x v="43"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6534,7 +6768,7 @@
   </r>
   <r>
     <n v="267"/>
-    <d v="2025-11-14T00:00:00"/>
+    <x v="43"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6546,7 +6780,7 @@
   </r>
   <r>
     <n v="268"/>
-    <d v="2025-11-14T00:00:00"/>
+    <x v="43"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6558,7 +6792,7 @@
   </r>
   <r>
     <n v="272"/>
-    <d v="2025-11-17T00:00:00"/>
+    <x v="44"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6570,7 +6804,7 @@
   </r>
   <r>
     <n v="272"/>
-    <d v="2025-11-17T00:00:00"/>
+    <x v="44"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6582,7 +6816,7 @@
   </r>
   <r>
     <n v="272"/>
-    <d v="2025-11-17T00:00:00"/>
+    <x v="44"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6594,7 +6828,7 @@
   </r>
   <r>
     <n v="272"/>
-    <d v="2025-11-17T00:00:00"/>
+    <x v="44"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6606,7 +6840,7 @@
   </r>
   <r>
     <n v="272"/>
-    <d v="2025-11-17T00:00:00"/>
+    <x v="44"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6618,7 +6852,7 @@
   </r>
   <r>
     <n v="276"/>
-    <d v="2025-11-18T00:00:00"/>
+    <x v="45"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6630,7 +6864,7 @@
   </r>
   <r>
     <n v="276"/>
-    <d v="2025-11-18T00:00:00"/>
+    <x v="45"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6642,7 +6876,7 @@
   </r>
   <r>
     <n v="276"/>
-    <d v="2025-11-18T00:00:00"/>
+    <x v="45"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6654,7 +6888,7 @@
   </r>
   <r>
     <n v="278"/>
-    <d v="2025-11-19T00:00:00"/>
+    <x v="46"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -6666,7 +6900,7 @@
   </r>
   <r>
     <n v="278"/>
-    <d v="2025-11-19T00:00:00"/>
+    <x v="46"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6678,7 +6912,7 @@
   </r>
   <r>
     <n v="278"/>
-    <d v="2025-11-19T00:00:00"/>
+    <x v="46"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6690,7 +6924,7 @@
   </r>
   <r>
     <n v="283"/>
-    <d v="2025-11-21T00:00:00"/>
+    <x v="47"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6702,7 +6936,7 @@
   </r>
   <r>
     <n v="283"/>
-    <d v="2025-11-21T00:00:00"/>
+    <x v="47"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6714,7 +6948,7 @@
   </r>
   <r>
     <n v="283"/>
-    <d v="2025-11-21T00:00:00"/>
+    <x v="47"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6726,7 +6960,7 @@
   </r>
   <r>
     <n v="287"/>
-    <d v="2025-11-24T00:00:00"/>
+    <x v="48"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6738,7 +6972,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6750,7 +6984,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6762,7 +6996,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6774,7 +7008,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6786,7 +7020,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6798,7 +7032,7 @@
   </r>
   <r>
     <n v="288"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6810,7 +7044,7 @@
   </r>
   <r>
     <n v="289"/>
-    <d v="2025-11-24T00:00:00"/>
+    <x v="48"/>
     <x v="4"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -6822,7 +7056,7 @@
   </r>
   <r>
     <n v="290"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6834,7 +7068,7 @@
   </r>
   <r>
     <n v="290"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6846,7 +7080,7 @@
   </r>
   <r>
     <n v="292"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6858,7 +7092,7 @@
   </r>
   <r>
     <n v="292"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6870,7 +7104,7 @@
   </r>
   <r>
     <n v="292"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -6882,7 +7116,7 @@
   </r>
   <r>
     <n v="292"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6894,7 +7128,7 @@
   </r>
   <r>
     <n v="295"/>
-    <d v="2025-11-21T00:00:00"/>
+    <x v="47"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado."/>
@@ -6906,7 +7140,7 @@
   </r>
   <r>
     <n v="296"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6918,7 +7152,7 @@
   </r>
   <r>
     <n v="296"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6930,7 +7164,7 @@
   </r>
   <r>
     <n v="296"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6942,7 +7176,7 @@
   </r>
   <r>
     <n v="296"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -6954,7 +7188,7 @@
   </r>
   <r>
     <n v="296"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -6966,7 +7200,7 @@
   </r>
   <r>
     <n v="299"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6978,7 +7212,7 @@
   </r>
   <r>
     <n v="299"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -6990,7 +7224,7 @@
   </r>
   <r>
     <n v="299"/>
-    <d v="2025-11-26T00:00:00"/>
+    <x v="50"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7002,7 +7236,7 @@
   </r>
   <r>
     <n v="300"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7014,7 +7248,7 @@
   </r>
   <r>
     <n v="300"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7026,7 +7260,7 @@
   </r>
   <r>
     <n v="302"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7038,7 +7272,7 @@
   </r>
   <r>
     <n v="302"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7050,7 +7284,7 @@
   </r>
   <r>
     <n v="302"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7062,7 +7296,7 @@
   </r>
   <r>
     <n v="302"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7074,7 +7308,7 @@
   </r>
   <r>
     <n v="302"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7086,7 +7320,7 @@
   </r>
   <r>
     <n v="305"/>
-    <d v="2025-11-28T00:00:00"/>
+    <x v="52"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7098,7 +7332,7 @@
   </r>
   <r>
     <n v="306"/>
-    <d v="2025-12-01T00:00:00"/>
+    <x v="53"/>
     <x v="1"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7110,7 +7344,7 @@
   </r>
   <r>
     <n v="306"/>
-    <d v="2025-12-01T00:00:00"/>
+    <x v="53"/>
     <x v="1"/>
     <x v="11"/>
     <s v="Oficina We"/>
@@ -7122,7 +7356,7 @@
   </r>
   <r>
     <n v="308"/>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="54"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7134,7 +7368,7 @@
   </r>
   <r>
     <n v="309"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="8"/>
     <x v="9"/>
     <s v="APR Parcelación El Melón RP1"/>
@@ -7146,7 +7380,7 @@
   </r>
   <r>
     <n v="310"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="9"/>
     <x v="8"/>
     <s v="SSR Comité Manzanar"/>
@@ -7158,7 +7392,7 @@
   </r>
   <r>
     <n v="310"/>
-    <d v="2025-11-25T00:00:00"/>
+    <x v="49"/>
     <x v="9"/>
     <x v="8"/>
     <s v="SSR Comité Manzanar"/>
@@ -7170,7 +7404,7 @@
   </r>
   <r>
     <n v="311"/>
-    <d v="2025-11-27T00:00:00"/>
+    <x v="51"/>
     <x v="9"/>
     <x v="9"/>
     <s v="APR Carmen San José"/>
@@ -7182,7 +7416,7 @@
   </r>
   <r>
     <n v="312"/>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7194,7 +7428,7 @@
   </r>
   <r>
     <n v="312"/>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7206,7 +7440,7 @@
   </r>
   <r>
     <n v="312"/>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7218,7 +7452,7 @@
   </r>
   <r>
     <n v="312"/>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="54"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7230,7 +7464,7 @@
   </r>
   <r>
     <n v="313"/>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="55"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7242,7 +7476,7 @@
   </r>
   <r>
     <n v="313"/>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="55"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7254,7 +7488,7 @@
   </r>
   <r>
     <n v="313"/>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="55"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7266,7 +7500,7 @@
   </r>
   <r>
     <n v="313"/>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="55"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7278,7 +7512,7 @@
   </r>
   <r>
     <n v="314"/>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="55"/>
     <x v="1"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7290,7 +7524,7 @@
   </r>
   <r>
     <n v="315"/>
-    <d v="2025-12-04T00:00:00"/>
+    <x v="56"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7302,7 +7536,7 @@
   </r>
   <r>
     <n v="315"/>
-    <d v="2025-12-04T00:00:00"/>
+    <x v="56"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7314,7 +7548,7 @@
   </r>
   <r>
     <n v="318"/>
-    <d v="2025-12-05T00:00:00"/>
+    <x v="57"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7326,7 +7560,7 @@
   </r>
   <r>
     <n v="318"/>
-    <d v="2025-12-05T00:00:00"/>
+    <x v="57"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7338,7 +7572,7 @@
   </r>
   <r>
     <n v="320"/>
-    <d v="2025-12-10T00:00:00"/>
+    <x v="58"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7350,7 +7584,7 @@
   </r>
   <r>
     <n v="321"/>
-    <d v="2025-12-09T00:00:00"/>
+    <x v="59"/>
     <x v="2"/>
     <x v="9"/>
     <s v="APR Los Caleos"/>
@@ -7362,7 +7596,7 @@
   </r>
   <r>
     <n v="321"/>
-    <d v="2025-12-09T00:00:00"/>
+    <x v="59"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7374,7 +7608,7 @@
   </r>
   <r>
     <n v="325"/>
-    <d v="2025-12-11T00:00:00"/>
+    <x v="60"/>
     <x v="1"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7386,7 +7620,7 @@
   </r>
   <r>
     <n v="326"/>
-    <d v="2025-12-11T00:00:00"/>
+    <x v="60"/>
     <x v="2"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7398,7 +7632,7 @@
   </r>
   <r>
     <n v="327"/>
-    <d v="2025-12-05T00:00:00"/>
+    <x v="57"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7410,7 +7644,7 @@
   </r>
   <r>
     <n v="327"/>
-    <d v="2025-12-05T00:00:00"/>
+    <x v="57"/>
     <x v="1"/>
     <x v="1"/>
     <s v="AAES"/>
@@ -7422,7 +7656,7 @@
   </r>
   <r>
     <n v="330"/>
-    <d v="2025-12-11T00:00:00"/>
+    <x v="60"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7434,7 +7668,7 @@
   </r>
   <r>
     <n v="334"/>
-    <d v="2025-12-15T00:00:00"/>
+    <x v="61"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7446,7 +7680,7 @@
   </r>
   <r>
     <n v="336"/>
-    <d v="2025-12-16T00:00:00"/>
+    <x v="62"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7458,7 +7692,7 @@
   </r>
   <r>
     <n v="338"/>
-    <d v="2025-12-16T00:00:00"/>
+    <x v="62"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7470,7 +7704,7 @@
   </r>
   <r>
     <n v="338"/>
-    <d v="2025-12-16T00:00:00"/>
+    <x v="62"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7482,7 +7716,7 @@
   </r>
   <r>
     <n v="339"/>
-    <d v="2025-12-17T00:00:00"/>
+    <x v="63"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7494,7 +7728,7 @@
   </r>
   <r>
     <n v="339"/>
-    <d v="2025-12-17T00:00:00"/>
+    <x v="63"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7506,7 +7740,7 @@
   </r>
   <r>
     <n v="339"/>
-    <d v="2025-12-17T00:00:00"/>
+    <x v="63"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7518,7 +7752,7 @@
   </r>
   <r>
     <n v="339"/>
-    <d v="2025-12-17T00:00:00"/>
+    <x v="63"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7530,7 +7764,7 @@
   </r>
   <r>
     <n v="340"/>
-    <d v="2025-12-17T00:00:00"/>
+    <x v="63"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7542,7 +7776,7 @@
   </r>
   <r>
     <n v="341"/>
-    <d v="2025-12-18T00:00:00"/>
+    <x v="64"/>
     <x v="3"/>
     <x v="2"/>
     <s v="Los Bronces - Riecillos"/>
@@ -7554,7 +7788,7 @@
   </r>
   <r>
     <n v="342"/>
-    <d v="2025-12-19T00:00:00"/>
+    <x v="65"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7566,7 +7800,7 @@
   </r>
   <r>
     <n v="342"/>
-    <d v="2025-12-19T00:00:00"/>
+    <x v="65"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7578,7 +7812,7 @@
   </r>
   <r>
     <n v="345"/>
-    <d v="2025-12-23T00:00:00"/>
+    <x v="66"/>
     <x v="1"/>
     <x v="3"/>
     <s v="AALT DGA"/>
@@ -7590,7 +7824,7 @@
   </r>
   <r>
     <n v="347"/>
-    <d v="2025-12-22T00:00:00"/>
+    <x v="67"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7602,7 +7836,7 @@
   </r>
   <r>
     <n v="348"/>
-    <d v="2025-12-23T00:00:00"/>
+    <x v="66"/>
     <x v="0"/>
     <x v="0"/>
     <s v="ASP Pozos"/>
@@ -7614,7 +7848,7 @@
   </r>
   <r>
     <n v="349"/>
-    <d v="2025-12-23T00:00:00"/>
+    <x v="66"/>
     <x v="3"/>
     <x v="3"/>
     <s v="BN12"/>
@@ -7626,7 +7860,7 @@
   </r>
   <r>
     <n v="351"/>
-    <d v="2025-12-23T00:00:00"/>
+    <x v="66"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7638,7 +7872,7 @@
   </r>
   <r>
     <n v="351"/>
-    <d v="2025-12-23T00:00:00"/>
+    <x v="66"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7650,7 +7884,7 @@
   </r>
   <r>
     <n v="353"/>
-    <d v="2025-12-25T00:00:00"/>
+    <x v="68"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7662,7 +7896,7 @@
   </r>
   <r>
     <n v="355"/>
-    <d v="2025-12-26T00:00:00"/>
+    <x v="69"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7674,7 +7908,7 @@
   </r>
   <r>
     <n v="356"/>
-    <d v="2025-12-24T00:00:00"/>
+    <x v="70"/>
     <x v="3"/>
     <x v="3"/>
     <s v="Global Tórtolas"/>
@@ -7686,7 +7920,7 @@
   </r>
   <r>
     <n v="357"/>
-    <d v="2025-12-29T00:00:00"/>
+    <x v="71"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7698,7 +7932,7 @@
   </r>
   <r>
     <n v="357"/>
-    <d v="2025-12-29T00:00:00"/>
+    <x v="71"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7710,7 +7944,7 @@
   </r>
   <r>
     <n v="357"/>
-    <d v="2025-12-29T00:00:00"/>
+    <x v="71"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7722,7 +7956,7 @@
   </r>
   <r>
     <n v="361"/>
-    <d v="2025-12-30T00:00:00"/>
+    <x v="72"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7734,7 +7968,7 @@
   </r>
   <r>
     <n v="361"/>
-    <d v="2025-12-30T00:00:00"/>
+    <x v="72"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Calidad del Aire"/>
@@ -7746,7 +7980,7 @@
   </r>
   <r>
     <n v="365"/>
-    <d v="2025-12-31T00:00:00"/>
+    <x v="73"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7758,7 +7992,7 @@
   </r>
   <r>
     <n v="365"/>
-    <d v="2025-12-31T00:00:00"/>
+    <x v="73"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión hidrica el soldado "/>
@@ -7770,7 +8004,7 @@
   </r>
   <r>
     <n v="365"/>
-    <d v="2025-12-31T00:00:00"/>
+    <x v="73"/>
     <x v="5"/>
     <x v="1"/>
     <s v="Gestión Hídrica El Soldado"/>
@@ -7784,7 +8018,686 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F22:O34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="75">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="70"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item m="1" x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item m="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item m="1" x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="18">
+    <format dxfId="93">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="92">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="91">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="90">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="89">
+      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="88">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="87">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="86">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="85">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="84">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="83">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="82">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="81">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="80">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="79">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="77">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="76">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="2" selected="0">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="75">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="70"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item m="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item m="1" x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="20">
+    <format dxfId="113">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="112">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="111">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="110">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="109">
+      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="108">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="107">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="106">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="105">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="104">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="103">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="102">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="101">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="100">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="99">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="98">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="97">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="96">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="95">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="2" selected="0">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="94">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -7968,494 +8881,15 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="F22:O34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item m="1" x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item m="1" x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item m="1" x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="7"/>
-  </colFields>
-  <colItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="16">
-    <format dxfId="85">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="84">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="83">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="82">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="81">
-      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="80">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="79">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="78">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="77">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="76">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="75">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="74">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="73">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="72">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="71">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="70">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="270" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item m="1" x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item m="1" x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="7"/>
-  </colFields>
-  <colItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="18">
-    <format dxfId="103">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="102">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="101">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="100">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="99">
-      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="98">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="97">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="96">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="95">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="94">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="93">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="92">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="91">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="90">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="89">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="88">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="87">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="86">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD993EFB-D955-5C4E-A71F-DA84C3008DB7}" name="Tabla1" displayName="Tabla1" ref="A1:J251" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:J251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD993EFB-D955-5C4E-A71F-DA84C3008DB7}" name="Tabla1" displayName="Tabla1" ref="A1:J260" totalsRowShown="0" headerRowDxfId="115">
+  <autoFilter ref="A1:J260" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J251">
     <sortCondition ref="A1:A251"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6DD74F18-117A-EE4B-8437-4D852508B413}" name="OT"/>
-    <tableColumn id="2" xr3:uid="{AC558773-13A8-3048-A577-0E4AC7D5F8AC}" name="Fecha" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{AC558773-13A8-3048-A577-0E4AC7D5F8AC}" name="Fecha" dataDxfId="114"/>
     <tableColumn id="3" xr3:uid="{79DD1F73-91E5-234C-B201-3293AC0C4C8A}" name="Técnico"/>
     <tableColumn id="4" xr3:uid="{FC81FE9D-F306-0D4A-BF0C-AA6091B1C2E3}" name="Cliente"/>
     <tableColumn id="5" xr3:uid="{951FF7CA-73A7-C14A-93D5-BEF519DFDEAA}" name="Proyecto"/>
@@ -8754,7 +9188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.83203125" style="4"/>
@@ -16737,6 +17171,294 @@
         <v>505</v>
       </c>
     </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>372</v>
+      </c>
+      <c r="B252" s="4">
+        <v>46028</v>
+      </c>
+      <c r="C252" t="s">
+        <v>20</v>
+      </c>
+      <c r="D252" t="s">
+        <v>209</v>
+      </c>
+      <c r="E252" t="s">
+        <v>209</v>
+      </c>
+      <c r="F252" t="s">
+        <v>506</v>
+      </c>
+      <c r="G252" t="s">
+        <v>10</v>
+      </c>
+      <c r="H252" t="s">
+        <v>15</v>
+      </c>
+      <c r="I252" t="s">
+        <v>209</v>
+      </c>
+      <c r="J252" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>373</v>
+      </c>
+      <c r="B253" s="4">
+        <v>46029</v>
+      </c>
+      <c r="C253" t="s">
+        <v>20</v>
+      </c>
+      <c r="D253" t="s">
+        <v>209</v>
+      </c>
+      <c r="E253" t="s">
+        <v>62</v>
+      </c>
+      <c r="F253" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253" t="s">
+        <v>25</v>
+      </c>
+      <c r="I253" t="s">
+        <v>13</v>
+      </c>
+      <c r="J253" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>374</v>
+      </c>
+      <c r="B254" s="4">
+        <v>46029</v>
+      </c>
+      <c r="C254" t="s">
+        <v>43</v>
+      </c>
+      <c r="D254" t="s">
+        <v>256</v>
+      </c>
+      <c r="E254" t="s">
+        <v>21</v>
+      </c>
+      <c r="F254" t="s">
+        <v>44</v>
+      </c>
+      <c r="G254" t="s">
+        <v>10</v>
+      </c>
+      <c r="H254" t="s">
+        <v>25</v>
+      </c>
+      <c r="I254" t="s">
+        <v>509</v>
+      </c>
+      <c r="J254" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>376</v>
+      </c>
+      <c r="B255" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C255" t="s">
+        <v>43</v>
+      </c>
+      <c r="D255" t="s">
+        <v>254</v>
+      </c>
+      <c r="E255" t="s">
+        <v>48</v>
+      </c>
+      <c r="F255" t="s">
+        <v>49</v>
+      </c>
+      <c r="G255" t="s">
+        <v>10</v>
+      </c>
+      <c r="H255" t="s">
+        <v>45</v>
+      </c>
+      <c r="I255" t="s">
+        <v>510</v>
+      </c>
+      <c r="J255" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>376</v>
+      </c>
+      <c r="B256" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C256" t="s">
+        <v>43</v>
+      </c>
+      <c r="D256" t="s">
+        <v>254</v>
+      </c>
+      <c r="E256" t="s">
+        <v>48</v>
+      </c>
+      <c r="F256" t="s">
+        <v>511</v>
+      </c>
+      <c r="G256" t="s">
+        <v>10</v>
+      </c>
+      <c r="H256" t="s">
+        <v>45</v>
+      </c>
+      <c r="I256" t="s">
+        <v>510</v>
+      </c>
+      <c r="J256" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>376</v>
+      </c>
+      <c r="B257" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C257" t="s">
+        <v>43</v>
+      </c>
+      <c r="D257" t="s">
+        <v>254</v>
+      </c>
+      <c r="E257" t="s">
+        <v>48</v>
+      </c>
+      <c r="F257" t="s">
+        <v>194</v>
+      </c>
+      <c r="G257" t="s">
+        <v>10</v>
+      </c>
+      <c r="H257" t="s">
+        <v>45</v>
+      </c>
+      <c r="I257" t="s">
+        <v>510</v>
+      </c>
+      <c r="J257" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>376</v>
+      </c>
+      <c r="B258" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C258" t="s">
+        <v>43</v>
+      </c>
+      <c r="D258" t="s">
+        <v>254</v>
+      </c>
+      <c r="E258" t="s">
+        <v>48</v>
+      </c>
+      <c r="F258" t="s">
+        <v>512</v>
+      </c>
+      <c r="G258" t="s">
+        <v>10</v>
+      </c>
+      <c r="H258" t="s">
+        <v>45</v>
+      </c>
+      <c r="I258" t="s">
+        <v>510</v>
+      </c>
+      <c r="J258" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>377</v>
+      </c>
+      <c r="B259" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C259" t="s">
+        <v>20</v>
+      </c>
+      <c r="D259" t="s">
+        <v>209</v>
+      </c>
+      <c r="E259" t="s">
+        <v>209</v>
+      </c>
+      <c r="F259" t="s">
+        <v>513</v>
+      </c>
+      <c r="G259" t="s">
+        <v>10</v>
+      </c>
+      <c r="H259" t="s">
+        <v>11</v>
+      </c>
+      <c r="I259" t="s">
+        <v>12</v>
+      </c>
+      <c r="J259" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>377</v>
+      </c>
+      <c r="B260" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C260" t="s">
+        <v>20</v>
+      </c>
+      <c r="D260" t="s">
+        <v>258</v>
+      </c>
+      <c r="E260" t="s">
+        <v>208</v>
+      </c>
+      <c r="F260" t="s">
+        <v>514</v>
+      </c>
+      <c r="G260" t="s">
+        <v>10</v>
+      </c>
+      <c r="H260" t="s">
+        <v>60</v>
+      </c>
+      <c r="I260" t="s">
+        <v>12</v>
+      </c>
+      <c r="J260" t="s">
+        <v>520</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -16747,7 +17469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4232116A-91F5-B54C-9044-0B3E733911E3}">
-  <dimension ref="A2:AH90"/>
+  <dimension ref="A1:AH90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -16766,6 +17488,14 @@
     <col min="31" max="31" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="F1" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>521</v>
+      </c>
+    </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
@@ -16871,7 +17601,7 @@
       <c r="N5" s="26">
         <v>1</v>
       </c>
-      <c r="O5" s="30">
+      <c r="O5" s="31">
         <v>172</v>
       </c>
     </row>
@@ -16885,29 +17615,29 @@
       <c r="F6" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <v>4</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <v>8</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="32">
         <v>5</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="32">
         <v>1</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="32">
         <v>11</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="32">
         <v>1</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="32">
         <v>2</v>
       </c>
-      <c r="N6" s="31"/>
-      <c r="O6" s="32">
+      <c r="N6" s="32"/>
+      <c r="O6" s="33">
         <v>32</v>
       </c>
     </row>
@@ -16921,25 +17651,25 @@
       <c r="F7" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <v>5</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="34">
         <v>3</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="34">
         <v>5</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="34">
         <v>5</v>
       </c>
-      <c r="K7" s="33">
+      <c r="K7" s="34">
         <v>7</v>
       </c>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="34">
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="35">
         <v>25</v>
       </c>
     </row>
@@ -17157,16 +17887,16 @@
       <c r="H17" s="22">
         <v>28</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="30">
         <v>22</v>
       </c>
       <c r="J17" s="22">
         <v>29</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="30">
         <v>40</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="30">
         <v>92</v>
       </c>
       <c r="M17" s="22">
@@ -17177,6 +17907,14 @@
       </c>
       <c r="O17" s="25">
         <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="6:15" x14ac:dyDescent="0.2">
+      <c r="F20" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="22" spans="6:15" x14ac:dyDescent="0.2">
@@ -17482,16 +18220,16 @@
       <c r="H34" s="22">
         <v>28</v>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="30">
         <v>22</v>
       </c>
       <c r="J34" s="22">
         <v>29</v>
       </c>
-      <c r="K34" s="22">
+      <c r="K34" s="30">
         <v>40</v>
       </c>
-      <c r="L34" s="22">
+      <c r="L34" s="30">
         <v>92</v>
       </c>
       <c r="M34" s="22">

--- a/reasignacion_st_detallada.xlsx
+++ b/reasignacion_st_detallada.xlsx
@@ -2,26 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DC27CE-7679-D841-934A-F95030D3540E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C5C0F7-36F6-FD43-9DD6-D01459B02E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="-5560" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="600" windowWidth="28920" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reclasifiación ST" sheetId="1" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" r:id="rId2"/>
+    <sheet name="Detalle1" sheetId="4" r:id="rId2"/>
+    <sheet name="Detalle2" sheetId="5" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'reclasifiación ST'!$A$1:$J$260</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="524">
   <si>
     <t>OT</t>
   </si>
@@ -1939,6 +1941,12 @@
   </si>
   <si>
     <t>(Todas)</t>
+  </si>
+  <si>
+    <t>Detalles de Cuenta de Tipo de trabajo anterior - Técnico: Matías Pomar, Tipo de trabajo nuevo: MC, Fecha: 8/25/2025 (+)</t>
+  </si>
+  <si>
+    <t>Detalles de Cuenta de Tipo de trabajo anterior - Técnico: Tomás Bustamante, Tipo de trabajo nuevo: MC, Fecha: 8/25/2025 (+)</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2155,842 +2163,71 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="43">
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
       <fill>
@@ -3158,6 +2395,157 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
@@ -3209,10 +2597,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="108"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="8"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -3241,7 +2629,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Reclasifiación de ST</a:t>
+              <a:t>Distribución de trabajos dentro de "ST"</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3281,7 +2669,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3303,7 +2691,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -3324,9 +2714,9 @@
           </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
-          <c:showCatName val="1"/>
+          <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
@@ -3337,7 +2727,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3346,57 +2736,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="1.801017198333808E-2"/>
-              <c:y val="3.3324800589783236E-3"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3405,57 +2750,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-1.3869754182262298E-3"/>
-              <c:y val="4.7352307848280775E-3"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3464,57 +2764,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-2.2038146197227746E-2"/>
-              <c:y val="-2.3058752679503188E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3523,57 +2778,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="2.7147930085625126E-2"/>
-              <c:y val="1.9924394148468911E-3"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3582,57 +2792,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="1.57347365117767E-2"/>
-              <c:y val="-5.6860003711287715E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3641,57 +2806,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-5.6237108920905027E-2"/>
-              <c:y val="-2.6801608602416871E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3700,57 +2820,12 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-2.1177150660039154E-2"/>
-              <c:y val="-1.7559004719244323E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="es-CL"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -3763,8 +2838,10 @@
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -3779,12 +2856,25 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3801,10 +2891,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3821,10 +2912,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3841,10 +2933,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3861,10 +2954,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3881,6 +2975,7 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
@@ -3901,12 +2996,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3923,12 +3017,11 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -3943,206 +3036,6 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="2.7147930085625126E-2"/>
-                  <c:y val="1.9924394148468911E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="1.57347365117767E-2"/>
-                  <c:y val="-5.6860003711287715E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-5.6237108920905027E-2"/>
-                  <c:y val="-2.6801608602416871E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.1177150660039154E-2"/>
-                  <c:y val="-1.7559004719244323E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-2.2038146197227746E-2"/>
-                  <c:y val="-2.3058752679503188E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-1.3869754182262298E-3"/>
-                  <c:y val="4.7352307848280775E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-DEF4-114C-A44A-FAD1214694C9}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="1.801017198333808E-2"/>
-                  <c:y val="3.3324800589783236E-3"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000F-5BC5-BF4C-9D30-781F705AEBD1}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CL"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Resumen!$A$4:$A$12</c:f>
@@ -4217,14 +3110,221 @@
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
-          <c:showCatName val="1"/>
+          <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:gapWidth val="150"/>
+        <c:axId val="233276736"/>
+        <c:axId val="233278528"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="233276736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="233278528"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="233278528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Cantidad de</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-MX" baseline="0"/>
+                  <a:t> trabajos</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="233276736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -4278,8 +3378,8 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -4293,42 +3393,8 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
   <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -4855,16 +3921,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>77862</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>127533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>135466</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>792860</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>16774</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8018,7 +7084,536 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="10">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="75">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="59"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="67"/>
+        <item x="66"/>
+        <item x="70"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="14">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item m="1" x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="10">
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item m="1" x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="20">
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="2" selected="0">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
+  <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="10">
+        <item m="1" x="8"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de Fecha" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF17DA64-4947-1D48-9086-3623F421B77A}" name="TablaDinámica3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="F22:O34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -8232,41 +7827,41 @@
     <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="93">
+    <format dxfId="40">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="38">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="90">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="89">
+    <format dxfId="36">
       <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="35">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="33">
       <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="32">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="30">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8275,7 +7870,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -8284,7 +7879,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="28">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8293,7 +7888,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -8302,7 +7897,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="26">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1" selected="0">
@@ -8311,7 +7906,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -8320,7 +7915,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="24">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1" selected="0">
@@ -8329,7 +7924,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="23">
       <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="7" count="2" selected="0">
@@ -8352,544 +7947,26 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D15C8FBF-E86F-7E4D-8704-E287382FB22D}" name="TablaDinámica7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" grandTotalCaption="Total" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="F3:O17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="10">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" numFmtId="14" outline="0" showAll="0">
-      <items count="75">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="59"/>
-        <item x="58"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="67"/>
-        <item x="66"/>
-        <item x="70"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="14">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item m="1" x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="10">
-        <item x="2"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item m="1" x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="7"/>
-  </colFields>
-  <colItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Cuenta de Tipo de trabajo anterior" fld="6" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="20">
-    <format dxfId="113">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="112">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="111">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="110">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="109">
-      <pivotArea dataOnly="0" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="108">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="107">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="106">
-      <pivotArea grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="105">
-      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="104">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="103">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="102">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="101">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="100">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="99">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="98">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="97">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="96">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="95">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
-        <references count="1">
-          <reference field="7" count="2" selected="0">
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="94">
-      <pivotArea field="7" grandRow="1" outline="0" axis="axisCol" fieldPosition="0">
-        <references count="1">
-          <reference field="7" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47313AC0-AF55-864E-81F6-55385F412298}" name="TablaDinámica6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="10">
-        <item m="1" x="8"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cuenta de Fecha" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD993EFB-D955-5C4E-A71F-DA84C3008DB7}" name="Tabla1" displayName="Tabla1" ref="A1:J260" totalsRowShown="0" headerRowDxfId="115">
-  <autoFilter ref="A1:J260" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD993EFB-D955-5C4E-A71F-DA84C3008DB7}" name="Tabla1" displayName="Tabla1" ref="A1:J260" totalsRowShown="0" headerRowDxfId="42">
+  <autoFilter ref="A1:J260" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="[Los Bronces - Riecillos] R2700 Caudalimetro B"/>
+        <filter val="[Los Bronces - Riecillos] R2700 Gateway"/>
+        <filter val="[Los Bronces - Riecillos] R3050 Caudalimetro A"/>
+        <filter val="[Los Bronces - Riecillos] R3050 Caudalimetro C"/>
+        <filter val="[Los Bronces - Riecillos] R3050 Caudalimetro E"/>
+        <filter val="[Los Bronces - Riecillos] R3050 Gateway"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J251">
     <sortCondition ref="A1:A251"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6DD74F18-117A-EE4B-8437-4D852508B413}" name="OT"/>
-    <tableColumn id="2" xr3:uid="{AC558773-13A8-3048-A577-0E4AC7D5F8AC}" name="Fecha" dataDxfId="114"/>
+    <tableColumn id="2" xr3:uid="{AC558773-13A8-3048-A577-0E4AC7D5F8AC}" name="Fecha" dataDxfId="41"/>
     <tableColumn id="3" xr3:uid="{79DD1F73-91E5-234C-B201-3293AC0C4C8A}" name="Técnico"/>
     <tableColumn id="4" xr3:uid="{FC81FE9D-F306-0D4A-BF0C-AA6091B1C2E3}" name="Cliente"/>
     <tableColumn id="5" xr3:uid="{951FF7CA-73A7-C14A-93D5-BEF519DFDEAA}" name="Proyecto"/>
@@ -8900,6 +7977,44 @@
     <tableColumn id="10" xr3:uid="{3BCE3010-FC70-2547-95FC-57FAD7174575}" name="Resolución"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D311C619-E707-804B-B921-2987A4C8D5F2}" name="Tabla3" displayName="Tabla3" ref="A3:J4" totalsRowShown="0">
+  <autoFilter ref="A3:J4" xr:uid="{D311C619-E707-804B-B921-2987A4C8D5F2}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{F137B1B1-DF65-B245-9063-6FAFE224D506}" name="OT"/>
+    <tableColumn id="2" xr3:uid="{445418A4-396D-304F-8EE1-314097FF919D}" name="Fecha" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{154915F2-C9EA-FD4E-9669-049F2785259A}" name="Técnico"/>
+    <tableColumn id="4" xr3:uid="{CBA86BE4-3016-7D49-ACB4-A35205F463E8}" name="Cliente"/>
+    <tableColumn id="5" xr3:uid="{CB94478A-4F04-D845-8B50-AA7AE90CFED6}" name="Proyecto"/>
+    <tableColumn id="6" xr3:uid="{35426700-74A3-0341-8ABE-E51128FAADB5}" name="Asset"/>
+    <tableColumn id="7" xr3:uid="{F1ED83AD-0438-1A42-8847-72B0B80F093E}" name="Tipo de trabajo anterior"/>
+    <tableColumn id="8" xr3:uid="{D9033263-EEDC-944E-96E7-580A0726411E}" name="Tipo de trabajo nuevo"/>
+    <tableColumn id="9" xr3:uid="{0BD14F61-2A52-904D-BA4C-B11595CCB5FC}" name="Causa visita"/>
+    <tableColumn id="10" xr3:uid="{CCB1D230-447C-9240-811E-1B4A0F337356}" name="Resolución" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{89E52F2A-13A2-A44C-87CE-84D7B4E018FE}" name="Tabla4" displayName="Tabla4" ref="A3:J4" totalsRowShown="0">
+  <autoFilter ref="A3:J4" xr:uid="{89E52F2A-13A2-A44C-87CE-84D7B4E018FE}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{AFDC7D83-38D7-6647-A5A0-B155F94638A2}" name="OT"/>
+    <tableColumn id="2" xr3:uid="{B4661C83-FE21-2D4C-8B50-0505F1E0976C}" name="Fecha" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{7B5F32D5-10B3-D546-9933-9677C104F4FB}" name="Técnico"/>
+    <tableColumn id="4" xr3:uid="{1EF91B92-B59A-0E4B-964A-A80E9E056B8E}" name="Cliente"/>
+    <tableColumn id="5" xr3:uid="{1E2767A3-0A86-464A-9617-E8E116107259}" name="Proyecto"/>
+    <tableColumn id="6" xr3:uid="{CAAA43A4-DF57-7A45-99EE-866884BD459F}" name="Asset"/>
+    <tableColumn id="7" xr3:uid="{1C05265B-AF73-0644-993A-6C824AFCB0DD}" name="Tipo de trabajo anterior"/>
+    <tableColumn id="8" xr3:uid="{7200A967-0AFB-0643-BD3C-E0D02279EA9C}" name="Tipo de trabajo nuevo"/>
+    <tableColumn id="9" xr3:uid="{7FD78DDC-7F56-AA48-8D82-39F4093F373C}" name="Causa visita"/>
+    <tableColumn id="10" xr3:uid="{55DFB571-7003-2946-A7A2-6BC3FDC6AA66}" name="Resolución"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -9234,7 +8349,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>78</v>
       </c>
@@ -9266,7 +8381,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>81</v>
       </c>
@@ -9298,7 +8413,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>81</v>
       </c>
@@ -9330,7 +8445,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>83</v>
       </c>
@@ -9359,7 +8474,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>93</v>
       </c>
@@ -9391,7 +8506,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>93</v>
       </c>
@@ -9551,7 +8666,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>95</v>
       </c>
@@ -9583,7 +8698,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>96</v>
       </c>
@@ -9615,7 +8730,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>97</v>
       </c>
@@ -9647,7 +8762,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>101</v>
       </c>
@@ -9679,7 +8794,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>101</v>
       </c>
@@ -9711,7 +8826,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>101</v>
       </c>
@@ -9743,7 +8858,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>101</v>
       </c>
@@ -9775,7 +8890,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>101</v>
       </c>
@@ -9807,7 +8922,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>105</v>
       </c>
@@ -9839,7 +8954,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>105</v>
       </c>
@@ -9871,7 +8986,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>110</v>
       </c>
@@ -9903,7 +9018,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>110</v>
       </c>
@@ -9935,7 +9050,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>110</v>
       </c>
@@ -9967,7 +9082,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>111</v>
       </c>
@@ -9999,7 +9114,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>111</v>
       </c>
@@ -10031,7 +9146,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>111</v>
       </c>
@@ -10191,7 +9306,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>115</v>
       </c>
@@ -10219,11 +9334,11 @@
       <c r="I32" t="s">
         <v>182</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="35" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>117</v>
       </c>
@@ -10255,7 +9370,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>118</v>
       </c>
@@ -10287,7 +9402,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>118</v>
       </c>
@@ -10319,7 +9434,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>119</v>
       </c>
@@ -10351,7 +9466,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>123</v>
       </c>
@@ -10383,7 +9498,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>123</v>
       </c>
@@ -10415,7 +9530,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>126</v>
       </c>
@@ -10444,7 +9559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>126</v>
       </c>
@@ -10473,7 +9588,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>130</v>
       </c>
@@ -10505,7 +9620,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>130</v>
       </c>
@@ -10537,7 +9652,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>132</v>
       </c>
@@ -10569,7 +9684,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>143</v>
       </c>
@@ -10601,7 +9716,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>148</v>
       </c>
@@ -10630,7 +9745,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>148</v>
       </c>
@@ -10659,7 +9774,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>148</v>
       </c>
@@ -10688,7 +9803,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>148</v>
       </c>
@@ -10717,7 +9832,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>148</v>
       </c>
@@ -10746,7 +9861,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>148</v>
       </c>
@@ -10775,7 +9890,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>153</v>
       </c>
@@ -10807,7 +9922,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>153</v>
       </c>
@@ -10839,7 +9954,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>153</v>
       </c>
@@ -10871,7 +9986,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>155</v>
       </c>
@@ -10903,7 +10018,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>163</v>
       </c>
@@ -10935,7 +10050,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>163</v>
       </c>
@@ -10967,7 +10082,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>163</v>
       </c>
@@ -11031,7 +10146,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>166</v>
       </c>
@@ -11063,7 +10178,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>168</v>
       </c>
@@ -11092,7 +10207,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>172</v>
       </c>
@@ -11121,7 +10236,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>172</v>
       </c>
@@ -11150,7 +10265,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>172</v>
       </c>
@@ -11179,7 +10294,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>175</v>
       </c>
@@ -11211,7 +10326,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>175</v>
       </c>
@@ -11243,7 +10358,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>175</v>
       </c>
@@ -11275,7 +10390,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>175</v>
       </c>
@@ -11307,7 +10422,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>176</v>
       </c>
@@ -11339,7 +10454,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>176</v>
       </c>
@@ -11371,7 +10486,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>176</v>
       </c>
@@ -11403,7 +10518,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>179</v>
       </c>
@@ -11435,7 +10550,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>180</v>
       </c>
@@ -11467,7 +10582,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>182</v>
       </c>
@@ -11499,7 +10614,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>183</v>
       </c>
@@ -11531,7 +10646,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>187</v>
       </c>
@@ -11563,7 +10678,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>187</v>
       </c>
@@ -11595,7 +10710,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>187</v>
       </c>
@@ -11627,7 +10742,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>187</v>
       </c>
@@ -11659,7 +10774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>190</v>
       </c>
@@ -11691,7 +10806,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>191</v>
       </c>
@@ -11723,7 +10838,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>191</v>
       </c>
@@ -11755,7 +10870,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>191</v>
       </c>
@@ -11787,7 +10902,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>191</v>
       </c>
@@ -11819,7 +10934,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>192</v>
       </c>
@@ -11851,7 +10966,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>194</v>
       </c>
@@ -11883,7 +10998,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>196</v>
       </c>
@@ -11915,7 +11030,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>196</v>
       </c>
@@ -11947,7 +11062,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>196</v>
       </c>
@@ -11979,7 +11094,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>196</v>
       </c>
@@ -12011,7 +11126,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>199</v>
       </c>
@@ -12043,7 +11158,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>202</v>
       </c>
@@ -12075,7 +11190,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>205</v>
       </c>
@@ -12107,7 +11222,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>206</v>
       </c>
@@ -12139,7 +11254,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>213</v>
       </c>
@@ -12171,7 +11286,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>214</v>
       </c>
@@ -12203,7 +11318,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>217</v>
       </c>
@@ -12235,7 +11350,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>217</v>
       </c>
@@ -12267,7 +11382,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>217</v>
       </c>
@@ -12299,7 +11414,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>217</v>
       </c>
@@ -12331,7 +11446,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>217</v>
       </c>
@@ -12363,7 +11478,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>217</v>
       </c>
@@ -12395,7 +11510,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>219</v>
       </c>
@@ -12427,7 +11542,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>219</v>
       </c>
@@ -12459,7 +11574,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>219</v>
       </c>
@@ -12491,7 +11606,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>219</v>
       </c>
@@ -12523,7 +11638,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>223</v>
       </c>
@@ -12555,7 +11670,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>223</v>
       </c>
@@ -12587,7 +11702,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>223</v>
       </c>
@@ -12619,7 +11734,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>223</v>
       </c>
@@ -12683,7 +11798,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>233</v>
       </c>
@@ -12715,7 +11830,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>233</v>
       </c>
@@ -12747,7 +11862,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>233</v>
       </c>
@@ -12779,7 +11894,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>233</v>
       </c>
@@ -12811,7 +11926,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>234</v>
       </c>
@@ -12907,7 +12022,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>240</v>
       </c>
@@ -12939,7 +12054,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>240</v>
       </c>
@@ -12971,7 +12086,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>242</v>
       </c>
@@ -13003,7 +12118,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>242</v>
       </c>
@@ -13035,7 +12150,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>242</v>
       </c>
@@ -13067,7 +12182,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>242</v>
       </c>
@@ -13099,7 +12214,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>242</v>
       </c>
@@ -13131,7 +12246,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>244</v>
       </c>
@@ -13163,7 +12278,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>244</v>
       </c>
@@ -13195,7 +12310,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>246</v>
       </c>
@@ -13227,7 +12342,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>246</v>
       </c>
@@ -13259,7 +12374,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>249</v>
       </c>
@@ -13291,7 +12406,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>253</v>
       </c>
@@ -13323,7 +12438,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>253</v>
       </c>
@@ -13355,7 +12470,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>254</v>
       </c>
@@ -13451,7 +12566,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>258</v>
       </c>
@@ -13483,7 +12598,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>258</v>
       </c>
@@ -13515,7 +12630,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>260</v>
       </c>
@@ -13547,7 +12662,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>262</v>
       </c>
@@ -13579,7 +12694,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>262</v>
       </c>
@@ -13611,7 +12726,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>266</v>
       </c>
@@ -13643,7 +12758,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>266</v>
       </c>
@@ -13675,7 +12790,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>266</v>
       </c>
@@ -13707,7 +12822,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>266</v>
       </c>
@@ -13835,7 +12950,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>272</v>
       </c>
@@ -13867,7 +12982,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>272</v>
       </c>
@@ -13899,7 +13014,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>272</v>
       </c>
@@ -13931,7 +13046,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>272</v>
       </c>
@@ -13963,7 +13078,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>272</v>
       </c>
@@ -13995,7 +13110,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>276</v>
       </c>
@@ -14024,7 +13139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>276</v>
       </c>
@@ -14053,7 +13168,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>276</v>
       </c>
@@ -14085,7 +13200,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>278</v>
       </c>
@@ -14117,7 +13232,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>278</v>
       </c>
@@ -14149,7 +13264,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>278</v>
       </c>
@@ -14181,7 +13296,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>283</v>
       </c>
@@ -14213,7 +13328,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>283</v>
       </c>
@@ -14245,7 +13360,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>283</v>
       </c>
@@ -14309,7 +13424,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>288</v>
       </c>
@@ -14341,7 +13456,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>288</v>
       </c>
@@ -14373,7 +13488,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>288</v>
       </c>
@@ -14405,7 +13520,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>288</v>
       </c>
@@ -14437,7 +13552,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>288</v>
       </c>
@@ -14469,7 +13584,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>288</v>
       </c>
@@ -14501,7 +13616,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>289</v>
       </c>
@@ -14597,7 +13712,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>292</v>
       </c>
@@ -14629,7 +13744,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>292</v>
       </c>
@@ -14661,7 +13776,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>292</v>
       </c>
@@ -14693,7 +13808,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>292</v>
       </c>
@@ -14725,7 +13840,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>295</v>
       </c>
@@ -14757,7 +13872,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>296</v>
       </c>
@@ -14789,7 +13904,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>296</v>
       </c>
@@ -14821,7 +13936,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>296</v>
       </c>
@@ -14853,7 +13968,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>296</v>
       </c>
@@ -14885,7 +14000,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>296</v>
       </c>
@@ -15077,7 +14192,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>302</v>
       </c>
@@ -15109,7 +14224,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>302</v>
       </c>
@@ -15141,7 +14256,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>302</v>
       </c>
@@ -15173,7 +14288,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>302</v>
       </c>
@@ -15205,7 +14320,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>302</v>
       </c>
@@ -15237,7 +14352,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>305</v>
       </c>
@@ -15269,7 +14384,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>306</v>
       </c>
@@ -15301,7 +14416,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>306</v>
       </c>
@@ -15333,7 +14448,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>308</v>
       </c>
@@ -15365,7 +14480,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>309</v>
       </c>
@@ -15397,7 +14512,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>310</v>
       </c>
@@ -15429,7 +14544,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>310</v>
       </c>
@@ -15461,7 +14576,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>311</v>
       </c>
@@ -15493,7 +14608,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>312</v>
       </c>
@@ -15525,7 +14640,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>312</v>
       </c>
@@ -15557,7 +14672,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>312</v>
       </c>
@@ -15589,7 +14704,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>312</v>
       </c>
@@ -15621,7 +14736,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>313</v>
       </c>
@@ -15653,7 +14768,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>313</v>
       </c>
@@ -15685,7 +14800,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>313</v>
       </c>
@@ -15717,7 +14832,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>313</v>
       </c>
@@ -15749,7 +14864,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>314</v>
       </c>
@@ -15781,7 +14896,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>315</v>
       </c>
@@ -15813,7 +14928,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>315</v>
       </c>
@@ -15845,7 +14960,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>318</v>
       </c>
@@ -15877,7 +14992,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>318</v>
       </c>
@@ -15909,7 +15024,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>320</v>
       </c>
@@ -15941,7 +15056,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>321</v>
       </c>
@@ -15973,7 +15088,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>321</v>
       </c>
@@ -16037,7 +15152,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>326</v>
       </c>
@@ -16069,7 +15184,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>327</v>
       </c>
@@ -16101,7 +15216,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>327</v>
       </c>
@@ -16165,7 +15280,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>334</v>
       </c>
@@ -16229,7 +15344,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>338</v>
       </c>
@@ -16258,7 +15373,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>338</v>
       </c>
@@ -16287,7 +15402,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>339</v>
       </c>
@@ -16316,7 +15431,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>339</v>
       </c>
@@ -16345,7 +15460,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>339</v>
       </c>
@@ -16374,7 +15489,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>339</v>
       </c>
@@ -16467,7 +15582,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>342</v>
       </c>
@@ -16499,7 +15614,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>342</v>
       </c>
@@ -16531,7 +15646,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:10" s="17" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>345</v>
       </c>
@@ -16563,7 +15678,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>347</v>
       </c>
@@ -16595,7 +15710,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>348</v>
       </c>
@@ -16627,7 +15742,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>349</v>
       </c>
@@ -16659,7 +15774,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>351</v>
       </c>
@@ -16691,7 +15806,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>351</v>
       </c>
@@ -16723,7 +15838,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>353</v>
       </c>
@@ -16755,7 +15870,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>355</v>
       </c>
@@ -16787,7 +15902,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>356</v>
       </c>
@@ -16819,7 +15934,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>357</v>
       </c>
@@ -16851,7 +15966,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>357</v>
       </c>
@@ -16883,7 +15998,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>357</v>
       </c>
@@ -16915,7 +16030,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>361</v>
       </c>
@@ -16947,7 +16062,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>361</v>
       </c>
@@ -16979,7 +16094,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>365</v>
       </c>
@@ -17011,7 +16126,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>365</v>
       </c>
@@ -17043,7 +16158,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>365</v>
       </c>
@@ -17075,7 +16190,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>368</v>
       </c>
@@ -17107,7 +16222,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>368</v>
       </c>
@@ -17139,7 +16254,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>369</v>
       </c>
@@ -17171,7 +16286,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>372</v>
       </c>
@@ -17203,7 +16318,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>373</v>
       </c>
@@ -17267,7 +16382,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>376</v>
       </c>
@@ -17299,7 +16414,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>376</v>
       </c>
@@ -17331,7 +16446,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>376</v>
       </c>
@@ -17363,7 +16478,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>376</v>
       </c>
@@ -17395,7 +16510,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>377</v>
       </c>
@@ -17427,7 +16542,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>377</v>
       </c>
@@ -17468,6 +16583,191 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518FE350-5ED8-4B48-A506-7CE011BBDE61}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="36" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>309</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45988</v>
+      </c>
+      <c r="C4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>433</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E14B80-D144-AF46-9C28-4C2D6DE8B443}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="36" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>132</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45916</v>
+      </c>
+      <c r="C4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>170</v>
+      </c>
+      <c r="J4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4232116A-91F5-B54C-9044-0B3E733911E3}">
   <dimension ref="A1:AH90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -17533,7 +16833,7 @@
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4">
         <v>16</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -17571,37 +16871,37 @@
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5">
         <v>92</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="25">
         <v>9</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="25">
         <v>12</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="25">
         <v>11</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="25">
         <v>23</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="25">
         <v>13</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="25">
         <v>90</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="25">
         <v>13</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="25">
         <v>1</v>
       </c>
-      <c r="O5" s="31">
+      <c r="O5" s="30">
         <v>172</v>
       </c>
     </row>
@@ -17609,35 +16909,35 @@
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6">
         <v>40</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="31">
         <v>4</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="31">
         <v>8</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="31">
         <v>5</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="31">
         <v>1</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="31">
         <v>11</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="31">
         <v>1</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="31">
         <v>2</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33">
+      <c r="N6" s="31"/>
+      <c r="O6" s="32">
         <v>32</v>
       </c>
     </row>
@@ -17645,31 +16945,31 @@
       <c r="A7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7">
         <v>29</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="33">
         <v>5</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="33">
         <v>3</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="33">
         <v>5</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="33">
         <v>5</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="33">
         <v>7</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="35">
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="34">
         <v>25</v>
       </c>
     </row>
@@ -17677,23 +16977,23 @@
       <c r="A8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8">
         <v>22</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20">
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19">
         <v>1</v>
       </c>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="24">
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="23">
         <v>1</v>
       </c>
     </row>
@@ -17701,25 +17001,25 @@
       <c r="A9" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20">
+      <c r="G9" s="19"/>
+      <c r="H9" s="19">
         <v>1</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20">
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19">
         <v>1</v>
       </c>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="24">
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="23">
         <v>2</v>
       </c>
     </row>
@@ -17727,23 +17027,23 @@
       <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10">
         <v>28</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20">
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19">
         <v>1</v>
       </c>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="24">
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="23">
         <v>1</v>
       </c>
     </row>
@@ -17751,23 +17051,23 @@
       <c r="A11" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11">
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20">
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19">
         <v>1</v>
       </c>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="24">
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="23">
         <v>1</v>
       </c>
     </row>
@@ -17775,27 +17075,27 @@
       <c r="A12" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12">
         <v>247</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20">
+      <c r="G12" s="19"/>
+      <c r="H12" s="19">
         <v>2</v>
       </c>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20">
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19">
         <v>1</v>
       </c>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20">
+      <c r="L12" s="19"/>
+      <c r="M12" s="19">
         <v>1</v>
       </c>
-      <c r="N12" s="20"/>
-      <c r="O12" s="24">
+      <c r="N12" s="19"/>
+      <c r="O12" s="23">
         <v>4</v>
       </c>
     </row>
@@ -17803,19 +17103,19 @@
       <c r="F13" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19">
         <v>1</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20">
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19">
         <v>2</v>
       </c>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="24">
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="23">
         <v>3</v>
       </c>
     </row>
@@ -17823,21 +17123,21 @@
       <c r="F14" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19">
         <v>1</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="19">
         <v>1</v>
       </c>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20">
+      <c r="J14" s="19"/>
+      <c r="K14" s="19">
         <v>1</v>
       </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="24">
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="23">
         <v>3</v>
       </c>
     </row>
@@ -17845,17 +17145,17 @@
       <c r="F15" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20">
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19">
         <v>2</v>
       </c>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="24">
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="23">
         <v>2</v>
       </c>
     </row>
@@ -17863,17 +17163,17 @@
       <c r="F16" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="19">
         <v>1</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="24">
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="23">
         <v>1</v>
       </c>
     </row>
@@ -17881,31 +17181,31 @@
       <c r="F17" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="20">
         <v>19</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>28</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="29">
         <v>22</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="21">
         <v>29</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="29">
         <v>40</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="29">
         <v>92</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="21">
         <v>16</v>
       </c>
-      <c r="N17" s="22">
+      <c r="N17" s="21">
         <v>1</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="24">
         <v>247</v>
       </c>
     </row>
@@ -17969,25 +17269,25 @@
       <c r="F24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20">
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19">
         <v>2</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="19">
         <v>3</v>
       </c>
-      <c r="K24" s="20">
+      <c r="K24" s="19">
         <v>4</v>
       </c>
-      <c r="L24" s="20">
+      <c r="L24" s="19">
         <v>3</v>
       </c>
-      <c r="M24" s="20">
+      <c r="M24" s="19">
         <v>1</v>
       </c>
-      <c r="N24" s="20"/>
-      <c r="O24" s="23">
+      <c r="N24" s="19"/>
+      <c r="O24" s="22">
         <v>13</v>
       </c>
     </row>
@@ -17995,27 +17295,27 @@
       <c r="F25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="27">
         <v>2</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="27">
         <v>7</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="27">
         <v>7</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="27">
         <v>1</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="27">
         <v>12</v>
       </c>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28">
+      <c r="L25" s="27"/>
+      <c r="M25" s="27">
         <v>2</v>
       </c>
-      <c r="N25" s="28"/>
-      <c r="O25" s="29">
+      <c r="N25" s="27"/>
+      <c r="O25" s="28">
         <v>31</v>
       </c>
     </row>
@@ -18023,19 +17323,19 @@
       <c r="F26" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20">
+      <c r="G26" s="19"/>
+      <c r="H26" s="19">
         <v>3</v>
       </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20">
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19">
         <v>7</v>
       </c>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="24">
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="23">
         <v>10</v>
       </c>
     </row>
@@ -18043,27 +17343,27 @@
       <c r="F27" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="19">
         <v>3</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="19">
         <v>1</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20">
+      <c r="I27" s="19"/>
+      <c r="J27" s="19">
         <v>4</v>
       </c>
-      <c r="K27" s="20">
+      <c r="K27" s="19">
         <v>2</v>
       </c>
-      <c r="L27" s="20">
+      <c r="L27" s="19">
         <v>5</v>
       </c>
-      <c r="M27" s="20">
+      <c r="M27" s="19">
         <v>8</v>
       </c>
-      <c r="N27" s="20"/>
-      <c r="O27" s="24">
+      <c r="N27" s="19"/>
+      <c r="O27" s="23">
         <v>23</v>
       </c>
     </row>
@@ -18071,29 +17371,29 @@
       <c r="F28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="27">
         <v>8</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="27">
         <v>14</v>
       </c>
-      <c r="I28" s="28">
+      <c r="I28" s="27">
         <v>1</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="27">
         <v>6</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="27">
         <v>6</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="27">
         <v>17</v>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="27">
         <v>2</v>
       </c>
-      <c r="N28" s="28"/>
-      <c r="O28" s="29">
+      <c r="N28" s="27"/>
+      <c r="O28" s="28">
         <v>54</v>
       </c>
     </row>
@@ -18101,19 +17401,19 @@
       <c r="F29" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20">
+      <c r="G29" s="19"/>
+      <c r="H29" s="19">
         <v>2</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="19">
         <v>1</v>
       </c>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="24">
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="23">
         <v>3</v>
       </c>
     </row>
@@ -18121,21 +17421,21 @@
       <c r="F30" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <v>3</v>
       </c>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20">
+      <c r="H30" s="19"/>
+      <c r="I30" s="19">
         <v>2</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <v>1</v>
       </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="24">
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="23">
         <v>6</v>
       </c>
     </row>
@@ -18143,31 +17443,31 @@
       <c r="F31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="25">
         <v>3</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="25">
         <v>1</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="25">
         <v>9</v>
       </c>
-      <c r="J31" s="26">
+      <c r="J31" s="25">
         <v>14</v>
       </c>
-      <c r="K31" s="26">
+      <c r="K31" s="25">
         <v>7</v>
       </c>
-      <c r="L31" s="26">
+      <c r="L31" s="25">
         <v>67</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="25">
         <v>3</v>
       </c>
-      <c r="N31" s="26">
+      <c r="N31" s="25">
         <v>1</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="26">
         <v>105</v>
       </c>
     </row>
@@ -18175,17 +17475,17 @@
       <c r="F32" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20">
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19">
         <v>1</v>
       </c>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="24">
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="23">
         <v>1</v>
       </c>
     </row>
@@ -18193,17 +17493,17 @@
       <c r="F33" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20">
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19">
         <v>1</v>
       </c>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="24">
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="23">
         <v>1</v>
       </c>
       <c r="AH33" t="s">
@@ -18214,31 +17514,31 @@
       <c r="F34" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="20">
         <v>19</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="21">
         <v>28</v>
       </c>
-      <c r="I34" s="30">
+      <c r="I34" s="29">
         <v>22</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34" s="21">
         <v>29</v>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="29">
         <v>40</v>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="29">
         <v>92</v>
       </c>
-      <c r="M34" s="22">
+      <c r="M34" s="21">
         <v>16</v>
       </c>
-      <c r="N34" s="22">
+      <c r="N34" s="21">
         <v>1</v>
       </c>
-      <c r="O34" s="25">
+      <c r="O34" s="24">
         <v>247</v>
       </c>
     </row>
